--- a/web/scripts/channel-model-template/__fixtures__/sd-source-v1.xlsx
+++ b/web/scripts/channel-model-template/__fixtures__/sd-source-v1.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sd官价" sheetId="1" r:id="R3a9ca8e7ee1b4cc7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sd" sheetId="2" r:id="Re9025e5e38004baf"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="3" r:id="R5ff39510ca9748e5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sd官价" sheetId="1" r:id="Red5b3bdae9b7422a"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sd" sheetId="2" r:id="R224d10f6e7174fa1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="channel" sheetId="3" r:id="R668d2d3ef9564e85"/>
   </sheets>
 </workbook>
 </file>
@@ -109,9 +109,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="m-d"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
+    <numFmt numFmtId="200" formatCode="General"/>
+    <numFmt numFmtId="201" formatCode="0.000###"/>
+    <numFmt numFmtId="202" formatCode="0"/>
+    <numFmt numFmtId="203" formatCode="@"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -249,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom" wrapText="0"/>
     </xf>
@@ -406,6 +410,56 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="2" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="202" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="202" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="202" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="202" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="203" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="203" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="203" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2000,8 +2054,8 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R447f32532da44a06"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="Rd392e4ba4e3f4f90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R857c2ba7cb8c4778"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="R727f45d9e94f431f"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2214,7 +2268,7 @@
       <c r="F3" s="17" t="str">
         <v>seedance 720p-fast</v>
       </c>
-      <c r="G3" s="17" t="n">
+      <c r="G3" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H3" s="17" t="str">
@@ -2226,36 +2280,36 @@
       <c r="J3" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K3" s="20" t="n">
+      <c r="K3" s="71" t="n">
         <v>1.38</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M3" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" s="21" t="n">
+      <c r="M3" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P3" s="23" t="n">
+      <c r="P3" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q3" s="17"/>
-      <c r="R3" s="17" t="n">
+      <c r="R3" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S3" s="17" t="n">
+      <c r="S3" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T3" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U3" s="17" t="n">
-        <v>46127</v>
+      <c r="U3" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V3" s="17" t="str">
         <v>9:16</v>
@@ -2326,7 +2380,7 @@
       <c r="F4" s="17" t="str">
         <v>bb-seedance2.0 1080p-pro-gz-15s</v>
       </c>
-      <c r="G4" s="17" t="n">
+      <c r="G4" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H4" s="17" t="str">
@@ -2338,35 +2392,35 @@
       <c r="J4" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K4" s="20" t="n">
+      <c r="K4" s="71" t="n">
         <v>6.8</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O4" s="17" t="n">
+      <c r="M4" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N4" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O4" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P4" s="23" t="n">
+      <c r="P4" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q4" s="17"/>
-      <c r="R4" s="17" t="n">
+      <c r="R4" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S4" s="17" t="n">
+      <c r="S4" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T4" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U4" s="17" t="n">
+      <c r="U4" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V4" s="17" t="str">
@@ -2436,7 +2490,7 @@
       <c r="F5" s="17" t="str">
         <v>bb-seedance2.0 720p-fast-gz-15s</v>
       </c>
-      <c r="G5" s="17" t="n">
+      <c r="G5" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H5" s="17" t="str">
@@ -2448,35 +2502,35 @@
       <c r="J5" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K5" s="20" t="n">
+      <c r="K5" s="71" t="n">
         <v>4.68</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O5" s="17" t="n">
+      <c r="M5" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P5" s="23" t="n">
+      <c r="P5" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q5" s="17"/>
-      <c r="R5" s="17" t="n">
+      <c r="R5" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S5" s="17" t="n">
+      <c r="S5" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T5" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U5" s="17" t="n">
+      <c r="U5" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V5" s="17" t="str">
@@ -2546,7 +2600,7 @@
       <c r="F6" s="17" t="str">
         <v>bb-seedance2.0 720p-pro-gz-15s</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="17" t="str">
@@ -2558,35 +2612,35 @@
       <c r="J6" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K6" s="20" t="n">
+      <c r="K6" s="71" t="n">
         <v>5.58</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O6" s="17" t="n">
+      <c r="M6" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N6" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P6" s="23" t="n">
+      <c r="P6" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q6" s="17"/>
-      <c r="R6" s="17" t="n">
+      <c r="R6" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S6" s="17" t="n">
+      <c r="S6" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U6" s="17" t="n">
+      <c r="U6" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V6" s="17" t="str">
@@ -2656,7 +2710,7 @@
       <c r="F7" s="17" t="str">
         <v>mg-seedance2.0 -480p</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="17" t="str">
@@ -2668,36 +2722,36 @@
       <c r="J7" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K7" s="20" t="n">
+      <c r="K7" s="71" t="n">
         <v>0.268</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="17" t="n">
+      <c r="M7" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="21" t="n">
+      <c r="O7" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P7" s="17" t="n">
+      <c r="P7" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q7" s="17"/>
-      <c r="R7" s="17" t="n">
+      <c r="R7" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S7" s="17" t="n">
+      <c r="S7" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U7" s="17" t="n">
-        <v>46127</v>
+      <c r="U7" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V7" s="17" t="str">
         <v>不限</v>
@@ -2766,7 +2820,7 @@
       <c r="F8" s="17" t="str">
         <v>mg-seedance2.0 -480p fast</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="17" t="str">
@@ -2778,36 +2832,36 @@
       <c r="J8" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K8" s="20" t="n">
+      <c r="K8" s="71" t="n">
         <v>0.165</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M8" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" s="17" t="n">
+      <c r="M8" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="21" t="n">
+      <c r="O8" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P8" s="17" t="n">
+      <c r="P8" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q8" s="17"/>
-      <c r="R8" s="17" t="n">
+      <c r="R8" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S8" s="17" t="n">
+      <c r="S8" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U8" s="17" t="n">
-        <v>46127</v>
+      <c r="U8" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V8" s="17" t="str">
         <v>不限</v>
@@ -2876,7 +2930,7 @@
       <c r="F9" s="17" t="str">
         <v>mg-seedance2.0 -480p mini</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H9" s="17" t="str">
@@ -2888,36 +2942,36 @@
       <c r="J9" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" s="71" t="n">
         <v>0.128</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="17" t="n">
+      <c r="M9" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="21" t="n">
+      <c r="O9" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P9" s="17" t="n">
+      <c r="P9" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q9" s="17"/>
-      <c r="R9" s="17" t="n">
+      <c r="R9" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S9" s="17" t="n">
+      <c r="S9" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U9" s="17" t="n">
-        <v>46127</v>
+      <c r="U9" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V9" s="17" t="str">
         <v>不限</v>
@@ -2986,7 +3040,7 @@
       <c r="F10" s="17" t="str">
         <v>mg-seedance2.0 -720p fast</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H10" s="17" t="str">
@@ -2998,36 +3052,36 @@
       <c r="J10" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K10" s="20" t="n">
+      <c r="K10" s="71" t="n">
         <v>0.268</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" s="17" t="n">
+      <c r="M10" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="21" t="n">
+      <c r="O10" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P10" s="17" t="n">
+      <c r="P10" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q10" s="17"/>
-      <c r="R10" s="17" t="n">
+      <c r="R10" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S10" s="17" t="n">
+      <c r="S10" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U10" s="17" t="n">
-        <v>46127</v>
+      <c r="U10" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V10" s="17" t="str">
         <v>不限</v>
@@ -3096,7 +3150,7 @@
       <c r="F11" s="17" t="str">
         <v>mg-seedance2.0 -720p mini</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H11" s="17" t="str">
@@ -3108,36 +3162,36 @@
       <c r="J11" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="71" t="n">
         <v>0.198</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" s="17" t="n">
+      <c r="M11" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O11" s="21" t="n">
+      <c r="O11" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P11" s="17" t="n">
+      <c r="P11" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q11" s="17"/>
-      <c r="R11" s="17" t="n">
+      <c r="R11" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S11" s="17" t="n">
+      <c r="S11" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U11" s="17" t="n">
-        <v>46127</v>
+      <c r="U11" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V11" s="17" t="str">
         <v>不限</v>
@@ -3206,7 +3260,7 @@
       <c r="F12" s="17" t="str">
         <v>mg-seedance2.0 -720p pro</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H12" s="17" t="str">
@@ -3218,36 +3272,36 @@
       <c r="J12" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K12" s="20" t="n">
+      <c r="K12" s="71" t="n">
         <v>0.368</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M12" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" s="17" t="n">
+      <c r="M12" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O12" s="21" t="n">
+      <c r="O12" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P12" s="17" t="n">
+      <c r="P12" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q12" s="17"/>
-      <c r="R12" s="17" t="n">
+      <c r="R12" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S12" s="17" t="n">
+      <c r="S12" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U12" s="17" t="n">
-        <v>46127</v>
+      <c r="U12" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V12" s="17" t="str">
         <v>不限</v>
@@ -3306,37 +3360,37 @@
       <c r="D13" s="35"/>
       <c r="E13" s="17"/>
       <c r="F13" s="35"/>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H13" s="17"/>
       <c r="I13" s="35"/>
       <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="37" t="n">
+      <c r="K13" s="72"/>
+      <c r="L13" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="35"/>
-      <c r="R13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="35" t="n">
+      <c r="R13" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="35"/>
-      <c r="U13" s="35"/>
+      <c r="U13" s="85"/>
       <c r="V13" s="17"/>
       <c r="W13" s="35"/>
       <c r="X13" s="17">
@@ -3398,7 +3452,7 @@
       <c r="F14" s="17" t="str">
         <v>lec-seedance-2-0</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H14" s="17" t="str">
@@ -3410,35 +3464,35 @@
       <c r="J14" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K14" s="20" t="n">
+      <c r="K14" s="71" t="n">
         <v>2.3</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="17" t="n">
+      <c r="M14" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="P14" s="17" t="n">
+      <c r="P14" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="17"/>
-      <c r="R14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="17" t="n">
+      <c r="R14" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U14" s="17" t="str">
+      <c r="U14" s="84" t="str">
         <v>5,10,15</v>
       </c>
       <c r="V14" s="17" t="str">
@@ -3510,7 +3564,7 @@
       <c r="F15" s="17" t="str">
         <v>lec-seedance-fast-ht-720p</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H15" s="17" t="str">
@@ -3522,35 +3576,35 @@
       <c r="J15" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K15" s="20" t="n">
+      <c r="K15" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17" t="n">
+      <c r="M15" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="P15" s="17" t="n">
+      <c r="P15" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="17"/>
-      <c r="R15" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17" t="n">
+      <c r="R15" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U15" s="17" t="str">
+      <c r="U15" s="84" t="str">
         <v>10,15</v>
       </c>
       <c r="V15" s="17" t="str">
@@ -3622,7 +3676,7 @@
       <c r="F16" s="17" t="str">
         <v>lec-feituo-seedance-2-0-hn-fast-720p</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H16" s="17" t="str">
@@ -3634,35 +3688,35 @@
       <c r="J16" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K16" s="20" t="n">
+      <c r="K16" s="71" t="n">
         <v>4.3</v>
       </c>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M16" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" s="17" t="n">
+      <c r="M16" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N16" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O16" s="17" t="n">
+      <c r="O16" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P16" s="17" t="n">
+      <c r="P16" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q16" s="17"/>
-      <c r="R16" s="20" t="n">
+      <c r="R16" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S16" s="17" t="n">
+      <c r="S16" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U16" s="17" t="str">
+      <c r="U16" s="84" t="str">
         <v>5,10,15</v>
       </c>
       <c r="V16" s="17" t="str">
@@ -3732,7 +3786,7 @@
       <c r="F17" s="17" t="str">
         <v>lec-feituo-seedance-2-0-hn-720p</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="17" t="str">
@@ -3744,35 +3798,35 @@
       <c r="J17" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K17" s="20" t="n">
+      <c r="K17" s="71" t="n">
         <v>5.3</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M17" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" s="17" t="n">
+      <c r="M17" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="O17" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P17" s="23" t="n">
+      <c r="P17" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q17" s="17"/>
-      <c r="R17" s="20" t="n">
+      <c r="R17" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S17" s="17" t="n">
+      <c r="S17" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U17" s="17" t="str">
+      <c r="U17" s="84" t="str">
         <v>5,10,15</v>
       </c>
       <c r="V17" s="17" t="str">
@@ -3842,7 +3896,7 @@
       <c r="F18" s="17" t="str">
         <v>lec-feituo-seedance-2-0-ld-cvk-2</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="17" t="str">
@@ -3854,36 +3908,36 @@
       <c r="J18" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K18" s="20" t="n">
+      <c r="K18" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M18" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" s="21" t="n">
+      <c r="M18" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N18" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P18" s="23" t="n">
+      <c r="P18" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q18" s="17"/>
-      <c r="R18" s="20" t="n">
+      <c r="R18" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S18" s="17" t="n">
+      <c r="S18" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U18" s="17" t="n">
-        <v>46157</v>
+      <c r="U18" s="84" t="str">
+        <v>5-15</v>
       </c>
       <c r="V18" s="17" t="str">
         <v>不限</v>
@@ -3952,7 +4006,7 @@
       <c r="F19" s="17" t="str">
         <v>lec-feituo-seedance-2-0-limited-720p</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H19" s="17" t="str">
@@ -3964,36 +4018,36 @@
       <c r="J19" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K19" s="20" t="n">
+      <c r="K19" s="71" t="n">
         <v>0.25</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="21" t="n">
+      <c r="M19" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="P19" s="23" t="n">
+      <c r="P19" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="17"/>
-      <c r="R19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="17" t="n">
+      <c r="R19" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U19" s="17" t="n">
-        <v>46127</v>
+      <c r="U19" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V19" s="17" t="str">
         <v>不限</v>
@@ -4062,7 +4116,7 @@
       <c r="F20" s="17" t="str">
         <v>lec-feituo-seedance-2-0-lg-720p</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="17" t="str">
@@ -4074,36 +4128,36 @@
       <c r="J20" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="K20" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" s="21" t="n">
+      <c r="M20" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N20" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P20" s="23" t="n">
+      <c r="P20" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q20" s="17"/>
-      <c r="R20" s="20" t="n">
+      <c r="R20" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S20" s="17" t="n">
+      <c r="S20" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U20" s="17" t="n">
-        <v>46127</v>
+      <c r="U20" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V20" s="17" t="str">
         <v>不限</v>
@@ -4172,7 +4226,7 @@
       <c r="F21" s="17" t="str">
         <v>lec-feituo-seedance-2-0-my-fast-upscaled-1080p</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="17" t="str">
@@ -4184,36 +4238,36 @@
       <c r="J21" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K21" s="20" t="n">
+      <c r="K21" s="71" t="n">
         <v>3.8</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M21" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" s="17" t="n">
+      <c r="M21" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="21" t="n">
+      <c r="O21" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P21" s="23" t="n">
+      <c r="P21" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q21" s="17"/>
-      <c r="R21" s="20" t="n">
+      <c r="R21" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S21" s="17" t="n">
+      <c r="S21" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="17" t="str">
         <v>720</v>
       </c>
-      <c r="U21" s="17" t="n">
-        <v>46127</v>
+      <c r="U21" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V21" s="17" t="str">
         <v>不限</v>
@@ -4282,7 +4336,7 @@
       <c r="F22" s="17" t="str">
         <v>lec-feituo-seedance-2-0-my-upscaled-1080p</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H22" s="17" t="str">
@@ -4294,36 +4348,36 @@
       <c r="J22" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K22" s="20" t="n">
+      <c r="K22" s="71" t="n">
         <v>4.8</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M22" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" s="17" t="n">
+      <c r="M22" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N22" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O22" s="21" t="n">
+      <c r="O22" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P22" s="23" t="n">
+      <c r="P22" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q22" s="17"/>
-      <c r="R22" s="20" t="n">
+      <c r="R22" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S22" s="17" t="n">
+      <c r="S22" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="17" t="str">
         <v>720</v>
       </c>
-      <c r="U22" s="17" t="n">
-        <v>46127</v>
+      <c r="U22" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V22" s="17" t="str">
         <v>不限</v>
@@ -4392,7 +4446,7 @@
       <c r="F23" s="17" t="str">
         <v>lec-seedance-videos-standard</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H23" s="17" t="str">
@@ -4404,36 +4458,36 @@
       <c r="J23" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K23" s="20" t="n">
+      <c r="K23" s="71" t="n">
         <v>4.8</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M23" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" s="21" t="n">
+      <c r="M23" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N23" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P23" s="23" t="n">
+      <c r="P23" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q23" s="17"/>
-      <c r="R23" s="17" t="n">
+      <c r="R23" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S23" s="17" t="n">
+      <c r="S23" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U23" s="17" t="n">
-        <v>46127</v>
+      <c r="U23" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V23" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -4504,7 +4558,7 @@
       <c r="F24" s="17" t="str">
         <v>lec-seedance-videos-standard</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H24" s="17" t="str">
@@ -4516,36 +4570,36 @@
       <c r="J24" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K24" s="20" t="n">
+      <c r="K24" s="71" t="n">
         <v>5.8</v>
       </c>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M24" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O24" s="21" t="n">
+      <c r="M24" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N24" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O24" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P24" s="23" t="n">
+      <c r="P24" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q24" s="17"/>
-      <c r="R24" s="17" t="n">
+      <c r="R24" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S24" s="17" t="n">
+      <c r="S24" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U24" s="17" t="n">
-        <v>46127</v>
+      <c r="U24" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V24" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -4616,7 +4670,7 @@
       <c r="F25" s="17" t="str">
         <v>lec-seedance-videos-standard</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="17" t="str">
@@ -4628,36 +4682,36 @@
       <c r="J25" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K25" s="20" t="n">
+      <c r="K25" s="71" t="n">
         <v>0.6</v>
       </c>
-      <c r="L25" s="17" t="n">
+      <c r="L25" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" s="21" t="n">
+      <c r="M25" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P25" s="23" t="n">
+      <c r="P25" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q25" s="17"/>
-      <c r="R25" s="17" t="n">
+      <c r="R25" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S25" s="17" t="n">
+      <c r="S25" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U25" s="17" t="n">
-        <v>46127</v>
+      <c r="U25" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V25" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -4728,7 +4782,7 @@
       <c r="F26" s="17" t="str">
         <v>lec-seedance-videos-standard</v>
       </c>
-      <c r="G26" s="17" t="n">
+      <c r="G26" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="17" t="str">
@@ -4740,36 +4794,36 @@
       <c r="J26" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K26" s="20" t="n">
+      <c r="K26" s="71" t="n">
         <v>1.71</v>
       </c>
-      <c r="L26" s="17" t="n">
+      <c r="L26" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O26" s="21" t="n">
+      <c r="M26" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N26" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P26" s="23" t="n">
+      <c r="P26" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q26" s="17"/>
-      <c r="R26" s="17" t="n">
+      <c r="R26" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S26" s="17" t="n">
+      <c r="S26" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U26" s="17" t="n">
-        <v>46127</v>
+      <c r="U26" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V26" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -4840,7 +4894,7 @@
       <c r="F27" s="17" t="str">
         <v>lec-seedance-videos-fast</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H27" s="17" t="str">
@@ -4852,36 +4906,36 @@
       <c r="J27" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K27" s="20" t="n">
+      <c r="K27" s="71" t="n">
         <v>3.3</v>
       </c>
-      <c r="L27" s="17" t="n">
+      <c r="L27" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M27" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O27" s="21" t="n">
+      <c r="M27" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P27" s="23" t="n">
+      <c r="P27" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q27" s="17"/>
-      <c r="R27" s="17" t="n">
+      <c r="R27" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S27" s="17" t="n">
+      <c r="S27" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U27" s="17" t="n">
-        <v>46127</v>
+      <c r="U27" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V27" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -4952,7 +5006,7 @@
       <c r="F28" s="17" t="str">
         <v>lec-seedance-videos-fast</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="17" t="str">
@@ -4964,36 +5018,36 @@
       <c r="J28" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K28" s="20" t="n">
+      <c r="K28" s="71" t="n">
         <v>3.3</v>
       </c>
-      <c r="L28" s="17" t="n">
+      <c r="L28" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" s="21" t="n">
+      <c r="M28" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N28" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P28" s="23" t="n">
+      <c r="P28" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q28" s="17"/>
-      <c r="R28" s="17" t="n">
+      <c r="R28" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S28" s="17" t="n">
+      <c r="S28" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U28" s="17" t="n">
-        <v>46127</v>
+      <c r="U28" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V28" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5064,7 +5118,7 @@
       <c r="F29" s="17" t="str">
         <v>lec-seedance-videos-mini</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H29" s="17" t="str">
@@ -5076,36 +5130,36 @@
       <c r="J29" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K29" s="20" t="n">
+      <c r="K29" s="71" t="n">
         <v>2.3</v>
       </c>
-      <c r="L29" s="17" t="n">
+      <c r="L29" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M29" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O29" s="21" t="n">
+      <c r="M29" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O29" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P29" s="23" t="n">
+      <c r="P29" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q29" s="17"/>
-      <c r="R29" s="17" t="n">
+      <c r="R29" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S29" s="17" t="n">
+      <c r="S29" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U29" s="17" t="n">
-        <v>46127</v>
+      <c r="U29" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V29" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5176,7 +5230,7 @@
       <c r="F30" s="17" t="str">
         <v>lec-seedance-videos-mini</v>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="17" t="str">
@@ -5188,36 +5242,36 @@
       <c r="J30" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K30" s="20" t="n">
+      <c r="K30" s="71" t="n">
         <v>2.3</v>
       </c>
-      <c r="L30" s="17" t="n">
+      <c r="L30" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M30" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" s="21" t="n">
+      <c r="M30" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N30" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P30" s="23" t="n">
+      <c r="P30" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q30" s="17"/>
-      <c r="R30" s="17" t="n">
+      <c r="R30" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S30" s="17" t="n">
+      <c r="S30" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U30" s="17" t="n">
-        <v>46127</v>
+      <c r="U30" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V30" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5288,7 +5342,7 @@
       <c r="F31" s="17" t="str">
         <v>lec-seedance-videos-stable</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="17" t="str">
@@ -5300,36 +5354,36 @@
       <c r="J31" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K31" s="20" t="n">
+      <c r="K31" s="71" t="n">
         <v>0.27</v>
       </c>
-      <c r="L31" s="17" t="n">
+      <c r="L31" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M31" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="17" t="n">
+      <c r="M31" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O31" s="21" t="n">
+      <c r="O31" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P31" s="23" t="n">
+      <c r="P31" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q31" s="17"/>
-      <c r="R31" s="17" t="n">
+      <c r="R31" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S31" s="17" t="n">
+      <c r="S31" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U31" s="17" t="n">
-        <v>46127</v>
+      <c r="U31" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V31" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5400,7 +5454,7 @@
       <c r="F32" s="17" t="str">
         <v>lec-seedance-videos-stable</v>
       </c>
-      <c r="G32" s="17" t="n">
+      <c r="G32" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="17" t="str">
@@ -5412,36 +5466,36 @@
       <c r="J32" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K32" s="20" t="n">
+      <c r="K32" s="71" t="n">
         <v>0.37</v>
       </c>
-      <c r="L32" s="17" t="n">
+      <c r="L32" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M32" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" s="17" t="n">
+      <c r="M32" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N32" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O32" s="21" t="n">
+      <c r="O32" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P32" s="23" t="n">
+      <c r="P32" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q32" s="17"/>
-      <c r="R32" s="17" t="n">
+      <c r="R32" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S32" s="17" t="n">
+      <c r="S32" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U32" s="17" t="n">
-        <v>46127</v>
+      <c r="U32" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V32" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5512,7 +5566,7 @@
       <c r="F33" s="17" t="str">
         <v>lec-seedance-videos-stable-fast</v>
       </c>
-      <c r="G33" s="17" t="n">
+      <c r="G33" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="17" t="str">
@@ -5524,36 +5578,36 @@
       <c r="J33" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K33" s="20" t="n">
+      <c r="K33" s="71" t="n">
         <v>0.17</v>
       </c>
-      <c r="L33" s="17" t="n">
+      <c r="L33" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M33" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" s="17" t="n">
+      <c r="M33" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N33" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O33" s="21" t="n">
+      <c r="O33" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P33" s="23" t="n">
+      <c r="P33" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q33" s="17"/>
-      <c r="R33" s="17" t="n">
+      <c r="R33" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S33" s="17" t="n">
+      <c r="S33" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U33" s="17" t="n">
-        <v>46127</v>
+      <c r="U33" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V33" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5624,7 +5678,7 @@
       <c r="F34" s="17" t="str">
         <v>lec-seedance-videos-stable-fast</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="17" t="str">
@@ -5636,36 +5690,36 @@
       <c r="J34" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K34" s="20" t="n">
+      <c r="K34" s="71" t="n">
         <v>0.27</v>
       </c>
-      <c r="L34" s="17" t="n">
+      <c r="L34" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M34" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" s="17" t="n">
+      <c r="M34" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N34" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O34" s="21" t="n">
+      <c r="O34" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P34" s="23" t="n">
+      <c r="P34" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q34" s="17"/>
-      <c r="R34" s="17" t="n">
+      <c r="R34" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S34" s="17" t="n">
+      <c r="S34" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U34" s="17" t="n">
-        <v>46127</v>
+      <c r="U34" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V34" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5736,7 +5790,7 @@
       <c r="F35" s="17" t="str">
         <v>lec-seedance-videos-stable-mini</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="17" t="str">
@@ -5748,36 +5802,36 @@
       <c r="J35" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K35" s="20" t="n">
+      <c r="K35" s="71" t="n">
         <v>0.14</v>
       </c>
-      <c r="L35" s="17" t="n">
+      <c r="L35" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M35" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" s="17" t="n">
+      <c r="M35" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N35" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O35" s="21" t="n">
+      <c r="O35" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P35" s="23" t="n">
+      <c r="P35" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q35" s="17"/>
-      <c r="R35" s="17" t="n">
+      <c r="R35" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S35" s="17" t="n">
+      <c r="S35" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U35" s="17" t="n">
-        <v>46127</v>
+      <c r="U35" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V35" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5848,7 +5902,7 @@
       <c r="F36" s="17" t="str">
         <v>lec-seedance-videos-stable-mini</v>
       </c>
-      <c r="G36" s="17" t="n">
+      <c r="G36" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="17" t="str">
@@ -5860,36 +5914,36 @@
       <c r="J36" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K36" s="20" t="n">
+      <c r="K36" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="L36" s="17" t="n">
+      <c r="L36" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M36" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" s="17" t="n">
+      <c r="M36" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N36" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O36" s="21" t="n">
+      <c r="O36" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P36" s="23" t="n">
+      <c r="P36" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q36" s="17"/>
-      <c r="R36" s="17" t="n">
+      <c r="R36" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S36" s="17" t="n">
+      <c r="S36" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U36" s="17" t="n">
-        <v>46127</v>
+      <c r="U36" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V36" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -5960,7 +6014,7 @@
       <c r="F37" s="17" t="str">
         <v>lec-seedance-videos-stable-720p</v>
       </c>
-      <c r="G37" s="17" t="n">
+      <c r="G37" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H37" s="17" t="str">
@@ -5972,36 +6026,36 @@
       <c r="J37" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K37" s="20" t="n">
+      <c r="K37" s="71" t="n">
         <v>5.5</v>
       </c>
-      <c r="L37" s="17" t="n">
+      <c r="L37" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M37" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O37" s="21" t="n">
+      <c r="M37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N37" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P37" s="23" t="n">
+      <c r="P37" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q37" s="17"/>
-      <c r="R37" s="17" t="n">
+      <c r="R37" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S37" s="17" t="n">
+      <c r="S37" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U37" s="17" t="n">
-        <v>46127</v>
+      <c r="U37" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V37" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6072,7 +6126,7 @@
       <c r="F38" s="17" t="str">
         <v>lec-seedance-videos-fast-720p</v>
       </c>
-      <c r="G38" s="17" t="n">
+      <c r="G38" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="17" t="str">
@@ -6084,36 +6138,36 @@
       <c r="J38" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K38" s="20" t="n">
+      <c r="K38" s="71" t="n">
         <v>3.5</v>
       </c>
-      <c r="L38" s="17" t="n">
+      <c r="L38" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M38" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O38" s="21" t="n">
+      <c r="M38" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O38" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P38" s="23" t="n">
+      <c r="P38" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q38" s="17"/>
-      <c r="R38" s="17" t="n">
+      <c r="R38" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S38" s="17" t="n">
+      <c r="S38" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U38" s="17" t="n">
-        <v>46127</v>
+      <c r="U38" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V38" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6184,7 +6238,7 @@
       <c r="F39" s="17" t="str">
         <v>lec-seedance-videos-mini-720p</v>
       </c>
-      <c r="G39" s="17" t="n">
+      <c r="G39" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="17" t="str">
@@ -6196,36 +6250,36 @@
       <c r="J39" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K39" s="20" t="n">
+      <c r="K39" s="71" t="n">
         <v>2.8</v>
       </c>
-      <c r="L39" s="17" t="n">
+      <c r="L39" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M39" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O39" s="21" t="n">
+      <c r="M39" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N39" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O39" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P39" s="23" t="n">
+      <c r="P39" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q39" s="17"/>
-      <c r="R39" s="17" t="n">
+      <c r="R39" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S39" s="17" t="n">
+      <c r="S39" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U39" s="17" t="n">
-        <v>46127</v>
+      <c r="U39" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V39" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6296,7 +6350,7 @@
       <c r="F40" s="17" t="str">
         <v>lec-seedance-videos-face-standard</v>
       </c>
-      <c r="G40" s="17" t="n">
+      <c r="G40" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="17" t="str">
@@ -6308,36 +6362,36 @@
       <c r="J40" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K40" s="20" t="n">
+      <c r="K40" s="71" t="n">
         <v>3.5</v>
       </c>
-      <c r="L40" s="17" t="n">
+      <c r="L40" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M40" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" s="21" t="n">
+      <c r="M40" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N40" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P40" s="23" t="n">
+      <c r="P40" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q40" s="17"/>
-      <c r="R40" s="17" t="n">
+      <c r="R40" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S40" s="17" t="n">
+      <c r="S40" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U40" s="17" t="n">
-        <v>46127</v>
+      <c r="U40" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V40" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6408,7 +6462,7 @@
       <c r="F41" s="17" t="str">
         <v>lec-seedance-videos-face-standard</v>
       </c>
-      <c r="G41" s="17" t="n">
+      <c r="G41" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="17" t="str">
@@ -6420,36 +6474,36 @@
       <c r="J41" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K41" s="20" t="n">
+      <c r="K41" s="71" t="n">
         <v>4.5</v>
       </c>
-      <c r="L41" s="17" t="n">
+      <c r="L41" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M41" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O41" s="21" t="n">
+      <c r="M41" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N41" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O41" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P41" s="23" t="n">
+      <c r="P41" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q41" s="17"/>
-      <c r="R41" s="17" t="n">
+      <c r="R41" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S41" s="17" t="n">
+      <c r="S41" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U41" s="17" t="n">
-        <v>46127</v>
+      <c r="U41" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V41" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6520,7 +6574,7 @@
       <c r="F42" s="17" t="str">
         <v>lec-seedance-videos-face-standard</v>
       </c>
-      <c r="G42" s="17" t="n">
+      <c r="G42" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H42" s="17" t="str">
@@ -6532,36 +6586,36 @@
       <c r="J42" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K42" s="20" t="n">
+      <c r="K42" s="71" t="n">
         <v>0.52</v>
       </c>
-      <c r="L42" s="17" t="n">
+      <c r="L42" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M42" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O42" s="21" t="n">
+      <c r="M42" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N42" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P42" s="23" t="n">
+      <c r="P42" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q42" s="17"/>
-      <c r="R42" s="17" t="n">
+      <c r="R42" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S42" s="17" t="n">
+      <c r="S42" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U42" s="17" t="n">
-        <v>46127</v>
+      <c r="U42" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V42" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6632,7 +6686,7 @@
       <c r="F43" s="17" t="str">
         <v>lec-seedance-videos-face-fast</v>
       </c>
-      <c r="G43" s="17" t="n">
+      <c r="G43" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H43" s="17" t="str">
@@ -6644,36 +6698,36 @@
       <c r="J43" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K43" s="20" t="n">
+      <c r="K43" s="71" t="n">
         <v>2.3</v>
       </c>
-      <c r="L43" s="17" t="n">
+      <c r="L43" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M43" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N43" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O43" s="21" t="n">
+      <c r="M43" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N43" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P43" s="23" t="n">
+      <c r="P43" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q43" s="17"/>
-      <c r="R43" s="17" t="n">
+      <c r="R43" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S43" s="17" t="n">
+      <c r="S43" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U43" s="17" t="n">
-        <v>46127</v>
+      <c r="U43" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V43" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6744,7 +6798,7 @@
       <c r="F44" s="17" t="str">
         <v>lec-seedance-videos-face-fast</v>
       </c>
-      <c r="G44" s="17" t="n">
+      <c r="G44" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H44" s="17" t="str">
@@ -6756,36 +6810,36 @@
       <c r="J44" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K44" s="20" t="n">
+      <c r="K44" s="71" t="n">
         <v>3.3</v>
       </c>
-      <c r="L44" s="17" t="n">
+      <c r="L44" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M44" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N44" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O44" s="21" t="n">
+      <c r="M44" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N44" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P44" s="23" t="n">
+      <c r="P44" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q44" s="17"/>
-      <c r="R44" s="17" t="n">
+      <c r="R44" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S44" s="17" t="n">
+      <c r="S44" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U44" s="17" t="n">
-        <v>46127</v>
+      <c r="U44" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V44" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6856,7 +6910,7 @@
       <c r="F45" s="17" t="str">
         <v>lec-fd-seedance-2-0-933-720p</v>
       </c>
-      <c r="G45" s="17" t="n">
+      <c r="G45" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H45" s="17" t="str">
@@ -6868,36 +6922,36 @@
       <c r="J45" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K45" s="20" t="n">
+      <c r="K45" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="L45" s="17" t="n">
+      <c r="L45" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M45" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" s="21" t="n">
+      <c r="M45" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O45" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P45" s="23" t="n">
+      <c r="P45" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q45" s="17"/>
-      <c r="R45" s="17" t="n">
+      <c r="R45" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S45" s="17" t="n">
+      <c r="S45" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U45" s="17" t="n">
-        <v>46127</v>
+      <c r="U45" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V45" s="17" t="str">
         <v>9:16, 16:9, 1:1</v>
@@ -6956,37 +7010,37 @@
       <c r="D46" s="35"/>
       <c r="E46" s="17"/>
       <c r="F46" s="35"/>
-      <c r="G46" s="17" t="n">
+      <c r="G46" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="35"/>
       <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="37" t="n">
+      <c r="K46" s="72"/>
+      <c r="L46" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="35"/>
-      <c r="R46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="35" t="n">
+      <c r="R46" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="35"/>
-      <c r="U46" s="35"/>
+      <c r="U46" s="85"/>
       <c r="V46" s="17"/>
       <c r="W46" s="35"/>
       <c r="X46" s="17"/>
@@ -7032,7 +7086,7 @@
       <c r="F47" s="17" t="str">
         <v>seedance-720p-5s</v>
       </c>
-      <c r="G47" s="17" t="n">
+      <c r="G47" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H47" s="17" t="str">
@@ -7044,35 +7098,35 @@
       <c r="J47" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K47" s="20" t="n">
+      <c r="K47" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="L47" s="17" t="n">
+      <c r="L47" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M47" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N47" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O47" s="17" t="n">
+      <c r="M47" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O47" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P47" s="23" t="n">
+      <c r="P47" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q47" s="17"/>
-      <c r="R47" s="17" t="n">
+      <c r="R47" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S47" s="17" t="n">
+      <c r="S47" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U47" s="17" t="n">
+      <c r="U47" s="84" t="str">
         <v>5</v>
       </c>
       <c r="V47" s="17" t="str">
@@ -7146,7 +7200,7 @@
       <c r="F48" s="17" t="str">
         <v>seedance-720p-10s</v>
       </c>
-      <c r="G48" s="17" t="n">
+      <c r="G48" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H48" s="17" t="str">
@@ -7158,35 +7212,35 @@
       <c r="J48" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K48" s="20" t="n">
+      <c r="K48" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="17" t="n">
+      <c r="L48" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M48" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N48" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O48" s="17" t="n">
+      <c r="M48" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N48" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O48" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P48" s="23" t="n">
+      <c r="P48" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q48" s="17"/>
-      <c r="R48" s="17" t="n">
+      <c r="R48" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S48" s="17" t="n">
+      <c r="S48" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U48" s="17" t="n">
+      <c r="U48" s="84" t="str">
         <v>10</v>
       </c>
       <c r="V48" s="17" t="str">
@@ -7260,7 +7314,7 @@
       <c r="F49" s="17" t="str">
         <v>seedance-720p-15s</v>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H49" s="17" t="str">
@@ -7272,35 +7326,35 @@
       <c r="J49" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K49" s="20" t="n">
+      <c r="K49" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="17" t="n">
+      <c r="L49" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M49" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N49" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" s="17" t="n">
+      <c r="M49" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N49" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O49" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P49" s="23" t="n">
+      <c r="P49" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q49" s="17"/>
-      <c r="R49" s="17" t="n">
+      <c r="R49" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S49" s="17" t="n">
+      <c r="S49" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U49" s="17" t="n">
+      <c r="U49" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V49" s="17" t="str">
@@ -7374,7 +7428,7 @@
       <c r="F50" s="17" t="str">
         <v>seedance-480p-5s</v>
       </c>
-      <c r="G50" s="17" t="n">
+      <c r="G50" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H50" s="17" t="str">
@@ -7386,35 +7440,35 @@
       <c r="J50" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K50" s="20" t="n">
+      <c r="K50" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="L50" s="17" t="n">
+      <c r="L50" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M50" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N50" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O50" s="17" t="n">
+      <c r="M50" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P50" s="23" t="n">
+      <c r="P50" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q50" s="17"/>
-      <c r="R50" s="17" t="n">
+      <c r="R50" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S50" s="17" t="n">
+      <c r="S50" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U50" s="17" t="n">
+      <c r="U50" s="84" t="str">
         <v>5</v>
       </c>
       <c r="V50" s="17" t="str">
@@ -7488,7 +7542,7 @@
       <c r="F51" s="17" t="str">
         <v>seedance-480p-10s</v>
       </c>
-      <c r="G51" s="17" t="n">
+      <c r="G51" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H51" s="17" t="str">
@@ -7500,35 +7554,35 @@
       <c r="J51" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K51" s="20" t="n">
+      <c r="K51" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="L51" s="17" t="n">
+      <c r="L51" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M51" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O51" s="17" t="n">
+      <c r="M51" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P51" s="23" t="n">
+      <c r="P51" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q51" s="17"/>
-      <c r="R51" s="17" t="n">
+      <c r="R51" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S51" s="17" t="n">
+      <c r="S51" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U51" s="17" t="n">
+      <c r="U51" s="84" t="str">
         <v>10</v>
       </c>
       <c r="V51" s="17" t="str">
@@ -7602,7 +7656,7 @@
       <c r="F52" s="17" t="str">
         <v>seedance-480p-15s</v>
       </c>
-      <c r="G52" s="17" t="n">
+      <c r="G52" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H52" s="17" t="str">
@@ -7614,35 +7668,35 @@
       <c r="J52" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K52" s="20" t="n">
+      <c r="K52" s="71" t="n">
         <v>0.5</v>
       </c>
-      <c r="L52" s="17" t="n">
+      <c r="L52" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M52" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N52" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" s="17" t="n">
+      <c r="M52" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N52" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P52" s="23" t="n">
+      <c r="P52" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q52" s="17"/>
-      <c r="R52" s="17" t="n">
+      <c r="R52" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S52" s="17" t="n">
+      <c r="S52" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U52" s="17" t="n">
+      <c r="U52" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V52" s="17" t="str">
@@ -7716,7 +7770,7 @@
       <c r="F53" s="17" t="str">
         <v>seedance-1080p-5s</v>
       </c>
-      <c r="G53" s="17" t="n">
+      <c r="G53" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H53" s="17" t="str">
@@ -7728,35 +7782,35 @@
       <c r="J53" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K53" s="20" t="n">
+      <c r="K53" s="71" t="n">
         <v>2.5</v>
       </c>
-      <c r="L53" s="17" t="n">
+      <c r="L53" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M53" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N53" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O53" s="17" t="n">
+      <c r="M53" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N53" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O53" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P53" s="23" t="n">
+      <c r="P53" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q53" s="17"/>
-      <c r="R53" s="17" t="n">
+      <c r="R53" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S53" s="17" t="n">
+      <c r="S53" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U53" s="17" t="n">
+      <c r="U53" s="84" t="str">
         <v>5</v>
       </c>
       <c r="V53" s="17" t="str">
@@ -7830,7 +7884,7 @@
       <c r="F54" s="17" t="str">
         <v>seedance-1080p-10s</v>
       </c>
-      <c r="G54" s="17" t="n">
+      <c r="G54" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H54" s="17" t="str">
@@ -7842,35 +7896,35 @@
       <c r="J54" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K54" s="20" t="n">
+      <c r="K54" s="71" t="n">
         <v>2.5</v>
       </c>
-      <c r="L54" s="17" t="n">
+      <c r="L54" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M54" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N54" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O54" s="17" t="n">
+      <c r="M54" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N54" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O54" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P54" s="23" t="n">
+      <c r="P54" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q54" s="17"/>
-      <c r="R54" s="17" t="n">
+      <c r="R54" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S54" s="17" t="n">
+      <c r="S54" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U54" s="17" t="n">
+      <c r="U54" s="84" t="str">
         <v>10</v>
       </c>
       <c r="V54" s="17" t="str">
@@ -7944,7 +7998,7 @@
       <c r="F55" s="17" t="str">
         <v>seedance-1080p-15s</v>
       </c>
-      <c r="G55" s="17" t="n">
+      <c r="G55" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H55" s="17" t="str">
@@ -7956,35 +8010,35 @@
       <c r="J55" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K55" s="20" t="n">
+      <c r="K55" s="71" t="n">
         <v>2.5</v>
       </c>
-      <c r="L55" s="17" t="n">
+      <c r="L55" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M55" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O55" s="17" t="n">
+      <c r="M55" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O55" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P55" s="23" t="n">
+      <c r="P55" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q55" s="17"/>
-      <c r="R55" s="17" t="n">
+      <c r="R55" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S55" s="17" t="n">
+      <c r="S55" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U55" s="17" t="n">
+      <c r="U55" s="84" t="str">
         <v>15</v>
       </c>
       <c r="V55" s="17" t="str">
@@ -8058,7 +8112,7 @@
       <c r="F56" s="17" t="str">
         <v>seedance-480p-token</v>
       </c>
-      <c r="G56" s="17" t="n">
+      <c r="G56" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H56" s="17" t="str">
@@ -8070,36 +8124,36 @@
       <c r="J56" s="17" t="str">
         <v>token</v>
       </c>
-      <c r="K56" s="17" t="n">
+      <c r="K56" s="71" t="n">
         <v>46</v>
       </c>
-      <c r="L56" s="17" t="n">
+      <c r="L56" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M56" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N56" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O56" s="21" t="n">
+      <c r="M56" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N56" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O56" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P56" s="23" t="n">
+      <c r="P56" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q56" s="17"/>
-      <c r="R56" s="17" t="n">
+      <c r="R56" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S56" s="17" t="n">
+      <c r="S56" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U56" s="17" t="n">
-        <v>46127</v>
+      <c r="U56" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V56" s="17" t="str">
         <v>不限</v>
@@ -8172,7 +8226,7 @@
       <c r="F57" s="17" t="str">
         <v>seedance-720p-token</v>
       </c>
-      <c r="G57" s="17" t="n">
+      <c r="G57" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H57" s="17" t="str">
@@ -8184,36 +8238,36 @@
       <c r="J57" s="17" t="str">
         <v>token</v>
       </c>
-      <c r="K57" s="17" t="n">
+      <c r="K57" s="71" t="n">
         <v>46</v>
       </c>
-      <c r="L57" s="17" t="n">
+      <c r="L57" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M57" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O57" s="21" t="n">
+      <c r="M57" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O57" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P57" s="23" t="n">
+      <c r="P57" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q57" s="17"/>
-      <c r="R57" s="17" t="n">
+      <c r="R57" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S57" s="17" t="n">
+      <c r="S57" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U57" s="17" t="n">
-        <v>46127</v>
+      <c r="U57" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V57" s="17" t="str">
         <v>不限</v>
@@ -8286,7 +8340,7 @@
       <c r="F58" s="17" t="str">
         <v>seedance-1080p-token</v>
       </c>
-      <c r="G58" s="17" t="n">
+      <c r="G58" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H58" s="17" t="str">
@@ -8298,36 +8352,36 @@
       <c r="J58" s="17" t="str">
         <v>token</v>
       </c>
-      <c r="K58" s="17" t="n">
+      <c r="K58" s="71" t="n">
         <v>51</v>
       </c>
-      <c r="L58" s="17" t="n">
+      <c r="L58" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M58" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N58" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O58" s="21" t="n">
+      <c r="M58" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P58" s="23" t="n">
+      <c r="P58" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q58" s="17"/>
-      <c r="R58" s="17" t="n">
+      <c r="R58" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S58" s="17" t="n">
+      <c r="S58" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U58" s="17" t="n">
-        <v>46127</v>
+      <c r="U58" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V58" s="17" t="str">
         <v>不限</v>
@@ -8388,37 +8442,37 @@
       <c r="D59" s="35"/>
       <c r="E59" s="36"/>
       <c r="F59" s="35"/>
-      <c r="G59" s="36" t="n">
+      <c r="G59" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H59" s="17"/>
       <c r="I59" s="35"/>
       <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
-      <c r="L59" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" s="37" t="n">
+      <c r="K59" s="72"/>
+      <c r="L59" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="35"/>
-      <c r="R59" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" s="35" t="n">
+      <c r="R59" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T59" s="35"/>
-      <c r="U59" s="35"/>
+      <c r="U59" s="85"/>
       <c r="V59" s="36"/>
       <c r="W59" s="35"/>
       <c r="X59" s="36"/>
@@ -8464,7 +8518,7 @@
       <c r="F60" s="17" t="str">
         <v>seedance-2.0</v>
       </c>
-      <c r="G60" s="17" t="n">
+      <c r="G60" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H60" s="17" t="str">
@@ -8476,36 +8530,36 @@
       <c r="J60" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K60" s="20" t="n">
+      <c r="K60" s="71" t="n">
         <v>5.005</v>
       </c>
-      <c r="L60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="23" t="n">
+      <c r="L60" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="17"/>
-      <c r="R60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="17" t="n">
+      <c r="R60" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T60" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U60" s="20" t="n">
-        <v>46127</v>
+      <c r="U60" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V60" s="17" t="str">
         <v>不限</v>
@@ -8574,7 +8628,7 @@
       <c r="F61" s="17" t="str">
         <v>seedance-2.0-1080p</v>
       </c>
-      <c r="G61" s="17" t="n">
+      <c r="G61" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H61" s="17" t="str">
@@ -8586,36 +8640,36 @@
       <c r="J61" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K61" s="20" t="n">
+      <c r="K61" s="71" t="n">
         <v>1.95</v>
       </c>
-      <c r="L61" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="23" t="n">
+      <c r="L61" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="17"/>
-      <c r="R61" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" s="17" t="n">
+      <c r="R61" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T61" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U61" s="20" t="n">
-        <v>46127</v>
+      <c r="U61" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V61" s="17" t="str">
         <v>不限</v>
@@ -8684,7 +8738,7 @@
       <c r="F62" s="17" t="str">
         <v>seedance-2.0-480p</v>
       </c>
-      <c r="G62" s="17" t="n">
+      <c r="G62" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H62" s="17" t="str">
@@ -8696,36 +8750,36 @@
       <c r="J62" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K62" s="20" t="n">
+      <c r="K62" s="71" t="n">
         <v>0.585</v>
       </c>
-      <c r="L62" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" s="23" t="n">
+      <c r="L62" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="17"/>
-      <c r="R62" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" s="17" t="n">
+      <c r="R62" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T62" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U62" s="20" t="n">
-        <v>46127</v>
+      <c r="U62" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V62" s="17" t="str">
         <v>不限</v>
@@ -8794,7 +8848,7 @@
       <c r="F63" s="17" t="str">
         <v>seedance-2.0-4k</v>
       </c>
-      <c r="G63" s="17" t="n">
+      <c r="G63" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H63" s="17" t="str">
@@ -8806,36 +8860,36 @@
       <c r="J63" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K63" s="20" t="n">
+      <c r="K63" s="71" t="n">
         <v>3.9</v>
       </c>
-      <c r="L63" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" s="23" t="n">
+      <c r="L63" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="17"/>
-      <c r="R63" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" s="17" t="n">
+      <c r="R63" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T63" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U63" s="20" t="n">
-        <v>46127</v>
+      <c r="U63" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V63" s="17" t="str">
         <v>不限</v>
@@ -8904,7 +8958,7 @@
       <c r="F64" s="17" t="str">
         <v>seedance-2.0-720p</v>
       </c>
-      <c r="G64" s="17" t="n">
+      <c r="G64" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="17" t="str">
@@ -8916,36 +8970,36 @@
       <c r="J64" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K64" s="20" t="n">
+      <c r="K64" s="71" t="n">
         <v>0.845</v>
       </c>
-      <c r="L64" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="23" t="n">
+      <c r="L64" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="17"/>
-      <c r="R64" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S64" s="17" t="n">
+      <c r="R64" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T64" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U64" s="20" t="n">
-        <v>46127</v>
+      <c r="U64" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V64" s="17" t="str">
         <v>不限</v>
@@ -9002,37 +9056,37 @@
       <c r="D65" s="35"/>
       <c r="E65" s="36"/>
       <c r="F65" s="35"/>
-      <c r="G65" s="36" t="n">
+      <c r="G65" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="35"/>
       <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" s="37" t="n">
+      <c r="K65" s="72"/>
+      <c r="L65" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="35"/>
-      <c r="R65" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="35" t="n">
+      <c r="R65" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T65" s="35"/>
-      <c r="U65" s="35"/>
+      <c r="U65" s="85"/>
       <c r="V65" s="36"/>
       <c r="W65" s="35"/>
       <c r="X65" s="36"/>
@@ -9078,7 +9132,7 @@
       <c r="F66" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G66" s="17" t="n">
+      <c r="G66" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H66" s="17" t="str">
@@ -9090,36 +9144,36 @@
       <c r="J66" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K66" s="20" t="n">
+      <c r="K66" s="71" t="n">
         <v>0.65</v>
       </c>
-      <c r="L66" s="17" t="n">
+      <c r="L66" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M66" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O66" s="21" t="n">
+      <c r="M66" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O66" s="76" t="n">
         <v>12</v>
       </c>
-      <c r="P66" s="23" t="n">
+      <c r="P66" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q66" s="17"/>
-      <c r="R66" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" s="17" t="n">
+      <c r="R66" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T66" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U66" s="20" t="n">
-        <v>46127</v>
+      <c r="U66" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V66" s="17" t="str">
         <v>不限</v>
@@ -9190,7 +9244,7 @@
       <c r="F67" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G67" s="17" t="n">
+      <c r="G67" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="17" t="str">
@@ -9202,36 +9256,36 @@
       <c r="J67" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K67" s="20" t="n">
+      <c r="K67" s="71" t="n">
         <v>6.8</v>
       </c>
-      <c r="L67" s="17" t="n">
+      <c r="L67" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M67" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N67" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O67" s="21" t="n">
+      <c r="M67" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O67" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P67" s="23" t="n">
+      <c r="P67" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q67" s="17"/>
-      <c r="R67" s="17" t="n">
+      <c r="R67" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S67" s="17" t="n">
+      <c r="S67" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T67" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U67" s="20" t="n">
-        <v>46127</v>
+      <c r="U67" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V67" s="17" t="str">
         <v>不限</v>
@@ -9300,7 +9354,7 @@
       <c r="F68" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G68" s="17" t="n">
+      <c r="G68" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="17" t="str">
@@ -9312,36 +9366,36 @@
       <c r="J68" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K68" s="20" t="n">
+      <c r="K68" s="71" t="n">
         <v>13.6</v>
       </c>
-      <c r="L68" s="17" t="n">
+      <c r="L68" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M68" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N68" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O68" s="21" t="n">
+      <c r="M68" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N68" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O68" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P68" s="23" t="n">
+      <c r="P68" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q68" s="17"/>
-      <c r="R68" s="17" t="n">
+      <c r="R68" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S68" s="17" t="n">
+      <c r="S68" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T68" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U68" s="20" t="n">
-        <v>46127</v>
+      <c r="U68" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V68" s="17" t="str">
         <v>不限</v>
@@ -9410,7 +9464,7 @@
       <c r="F69" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G69" s="17" t="n">
+      <c r="G69" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H69" s="17" t="str">
@@ -9422,36 +9476,36 @@
       <c r="J69" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K69" s="20" t="n">
+      <c r="K69" s="71" t="n">
         <v>27.2</v>
       </c>
-      <c r="L69" s="17" t="n">
+      <c r="L69" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M69" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N69" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O69" s="21" t="n">
+      <c r="M69" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N69" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O69" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P69" s="23" t="n">
+      <c r="P69" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q69" s="17"/>
-      <c r="R69" s="17" t="n">
+      <c r="R69" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S69" s="17" t="n">
+      <c r="S69" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T69" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U69" s="20" t="n">
-        <v>46127</v>
+      <c r="U69" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V69" s="17" t="str">
         <v>不限</v>
@@ -9520,7 +9574,7 @@
       <c r="F70" s="17" t="str">
         <v>video-2.0-fast</v>
       </c>
-      <c r="G70" s="17" t="n">
+      <c r="G70" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H70" s="17" t="str">
@@ -9532,36 +9586,36 @@
       <c r="J70" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K70" s="20" t="n">
+      <c r="K70" s="71" t="n">
         <v>5.8</v>
       </c>
-      <c r="L70" s="17" t="n">
+      <c r="L70" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M70" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N70" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O70" s="21" t="n">
+      <c r="M70" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N70" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O70" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P70" s="23" t="n">
+      <c r="P70" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q70" s="17"/>
-      <c r="R70" s="17" t="n">
+      <c r="R70" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S70" s="17" t="n">
+      <c r="S70" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T70" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U70" s="20" t="n">
-        <v>46127</v>
+      <c r="U70" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V70" s="17" t="str">
         <v>不限</v>
@@ -9630,7 +9684,7 @@
       <c r="F71" s="17" t="str">
         <v>video-2.0-mini</v>
       </c>
-      <c r="G71" s="17" t="n">
+      <c r="G71" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H71" s="17" t="str">
@@ -9642,36 +9696,36 @@
       <c r="J71" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K71" s="20" t="n">
+      <c r="K71" s="71" t="n">
         <v>4.9</v>
       </c>
-      <c r="L71" s="17" t="n">
+      <c r="L71" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M71" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N71" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O71" s="21" t="n">
+      <c r="M71" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N71" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O71" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P71" s="23" t="n">
+      <c r="P71" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q71" s="17"/>
-      <c r="R71" s="17" t="n">
+      <c r="R71" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S71" s="17" t="n">
+      <c r="S71" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U71" s="20" t="n">
-        <v>46127</v>
+      <c r="U71" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V71" s="17" t="str">
         <v>不限</v>
@@ -9740,7 +9794,7 @@
       <c r="F72" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G72" s="17" t="n">
+      <c r="G72" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H72" s="17" t="str">
@@ -9752,36 +9806,36 @@
       <c r="J72" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K72" s="20" t="n">
+      <c r="K72" s="71" t="n">
         <v>0.7</v>
       </c>
-      <c r="L72" s="17" t="n">
+      <c r="L72" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M72" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N72" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O72" s="21" t="n">
+      <c r="M72" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O72" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P72" s="23" t="n">
+      <c r="P72" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q72" s="17"/>
-      <c r="R72" s="17" t="n">
+      <c r="R72" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S72" s="17" t="n">
+      <c r="S72" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T72" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U72" s="20" t="n">
-        <v>46127</v>
+      <c r="U72" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V72" s="17" t="str">
         <v>不限</v>
@@ -9852,7 +9906,7 @@
       <c r="F73" s="17" t="str">
         <v>video-2.0-pro</v>
       </c>
-      <c r="G73" s="17" t="n">
+      <c r="G73" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H73" s="17" t="str">
@@ -9864,36 +9918,36 @@
       <c r="J73" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K73" s="20" t="n">
+      <c r="K73" s="71" t="n">
         <v>1.75</v>
       </c>
-      <c r="L73" s="17" t="n">
+      <c r="L73" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M73" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N73" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O73" s="21" t="n">
+      <c r="M73" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N73" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O73" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P73" s="23" t="n">
+      <c r="P73" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q73" s="17"/>
-      <c r="R73" s="17" t="n">
+      <c r="R73" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S73" s="17" t="n">
+      <c r="S73" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T73" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U73" s="20" t="n">
-        <v>46127</v>
+      <c r="U73" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V73" s="17" t="str">
         <v>不限</v>
@@ -9964,7 +10018,7 @@
       <c r="F74" s="17" t="str">
         <v>video-2.0-fast</v>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H74" s="17" t="str">
@@ -9976,36 +10030,36 @@
       <c r="J74" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K74" s="20" t="n">
+      <c r="K74" s="71" t="n">
         <v>0.56</v>
       </c>
-      <c r="L74" s="17" t="n">
+      <c r="L74" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M74" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N74" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O74" s="21" t="n">
+      <c r="M74" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N74" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O74" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P74" s="23" t="n">
+      <c r="P74" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q74" s="17"/>
-      <c r="R74" s="17" t="n">
+      <c r="R74" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S74" s="17" t="n">
+      <c r="S74" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T74" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U74" s="20" t="n">
-        <v>46127</v>
+      <c r="U74" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V74" s="17" t="str">
         <v>不限</v>
@@ -10076,7 +10130,7 @@
       <c r="F75" s="17" t="str">
         <v>video-2.0-mini</v>
       </c>
-      <c r="G75" s="17" t="n">
+      <c r="G75" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H75" s="17" t="str">
@@ -10088,36 +10142,36 @@
       <c r="J75" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K75" s="20" t="n">
+      <c r="K75" s="71" t="n">
         <v>0.48</v>
       </c>
-      <c r="L75" s="17" t="n">
+      <c r="L75" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M75" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N75" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O75" s="21" t="n">
+      <c r="M75" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N75" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O75" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P75" s="23" t="n">
+      <c r="P75" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q75" s="17"/>
-      <c r="R75" s="17" t="n">
+      <c r="R75" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S75" s="17" t="n">
+      <c r="S75" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U75" s="20" t="n">
-        <v>46127</v>
+      <c r="U75" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V75" s="17" t="str">
         <v>不限</v>
@@ -10176,37 +10230,37 @@
       <c r="D76" s="35"/>
       <c r="E76" s="36"/>
       <c r="F76" s="35"/>
-      <c r="G76" s="36" t="n">
+      <c r="G76" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="17"/>
       <c r="I76" s="35"/>
       <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" s="37" t="n">
+      <c r="K76" s="72"/>
+      <c r="L76" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="35"/>
-      <c r="R76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S76" s="35" t="n">
+      <c r="R76" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T76" s="35"/>
-      <c r="U76" s="35"/>
+      <c r="U76" s="85"/>
       <c r="V76" s="36"/>
       <c r="W76" s="35"/>
       <c r="X76" s="36"/>
@@ -10250,7 +10304,7 @@
       <c r="F77" s="17" t="str">
         <v>sd5-seedance-2.0</v>
       </c>
-      <c r="G77" s="17" t="n">
+      <c r="G77" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H77" s="17" t="str">
@@ -10262,36 +10316,36 @@
       <c r="J77" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K77" s="20" t="n">
+      <c r="K77" s="71" t="n">
         <v>3.85</v>
       </c>
-      <c r="L77" s="17" t="n">
+      <c r="L77" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M77" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N77" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O77" s="21" t="n">
+      <c r="M77" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N77" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P77" s="23" t="n">
+      <c r="P77" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q77" s="17"/>
-      <c r="R77" s="17" t="n">
+      <c r="R77" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S77" s="17" t="n">
+      <c r="S77" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T77" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U77" s="20" t="n">
-        <v>46127</v>
+      <c r="U77" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V77" s="17" t="str">
         <v>9:16, 16:9</v>
@@ -10358,7 +10412,7 @@
       <c r="F78" s="17" t="str">
         <v>sd5-seedance-2.0-fast</v>
       </c>
-      <c r="G78" s="17" t="n">
+      <c r="G78" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H78" s="17" t="str">
@@ -10370,36 +10424,36 @@
       <c r="J78" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K78" s="20" t="n">
+      <c r="K78" s="71" t="n">
         <v>2.6</v>
       </c>
-      <c r="L78" s="17" t="n">
+      <c r="L78" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M78" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N78" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O78" s="21" t="n">
+      <c r="M78" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N78" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O78" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P78" s="23" t="n">
+      <c r="P78" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q78" s="17"/>
-      <c r="R78" s="17" t="n">
+      <c r="R78" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S78" s="17" t="n">
+      <c r="S78" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T78" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U78" s="20" t="n">
-        <v>46127</v>
+      <c r="U78" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V78" s="17" t="str">
         <v>9:16, 16:9</v>
@@ -10466,7 +10520,7 @@
       <c r="F79" s="17" t="str">
         <v>seedance-2.0</v>
       </c>
-      <c r="G79" s="17" t="n">
+      <c r="G79" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H79" s="17" t="str">
@@ -10478,36 +10532,36 @@
       <c r="J79" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K79" s="20" t="n">
+      <c r="K79" s="71" t="n">
         <v>4.85</v>
       </c>
-      <c r="L79" s="17" t="n">
+      <c r="L79" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M79" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N79" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O79" s="21" t="n">
+      <c r="M79" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O79" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P79" s="23" t="n">
+      <c r="P79" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q79" s="17"/>
-      <c r="R79" s="17" t="n">
+      <c r="R79" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S79" s="17" t="n">
+      <c r="S79" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T79" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U79" s="20" t="n">
-        <v>46127</v>
+      <c r="U79" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V79" s="17" t="str">
         <v>不限</v>
@@ -10574,7 +10628,7 @@
       <c r="F80" s="17" t="str">
         <v>seedance-2.0-fast</v>
       </c>
-      <c r="G80" s="17" t="n">
+      <c r="G80" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="17" t="str">
@@ -10586,36 +10640,36 @@
       <c r="J80" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K80" s="20" t="n">
+      <c r="K80" s="71" t="n">
         <v>3.6</v>
       </c>
-      <c r="L80" s="17" t="n">
+      <c r="L80" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M80" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N80" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O80" s="21" t="n">
+      <c r="M80" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P80" s="23" t="n">
+      <c r="P80" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q80" s="17"/>
-      <c r="R80" s="17" t="n">
+      <c r="R80" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S80" s="17" t="n">
+      <c r="S80" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T80" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U80" s="20" t="n">
-        <v>46127</v>
+      <c r="U80" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V80" s="17" t="str">
         <v>不限</v>
@@ -10682,7 +10736,7 @@
       <c r="F81" s="17" t="str">
         <v>seedance-2.0-mini</v>
       </c>
-      <c r="G81" s="17" t="n">
+      <c r="G81" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H81" s="17" t="str">
@@ -10694,36 +10748,36 @@
       <c r="J81" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K81" s="20" t="n">
+      <c r="K81" s="71" t="n">
         <v>2.9</v>
       </c>
-      <c r="L81" s="17" t="n">
+      <c r="L81" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M81" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N81" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O81" s="21" t="n">
+      <c r="M81" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P81" s="23" t="n">
+      <c r="P81" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q81" s="17"/>
-      <c r="R81" s="17" t="n">
+      <c r="R81" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S81" s="17" t="n">
+      <c r="S81" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U81" s="20" t="n">
-        <v>46127</v>
+      <c r="U81" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V81" s="17" t="str">
         <v>不限</v>
@@ -10780,37 +10834,37 @@
       <c r="D82" s="35"/>
       <c r="E82" s="36"/>
       <c r="F82" s="35"/>
-      <c r="G82" s="36" t="n">
+      <c r="G82" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="35"/>
       <c r="J82" s="35"/>
-      <c r="K82" s="35"/>
-      <c r="L82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="37" t="n">
+      <c r="K82" s="72"/>
+      <c r="L82" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="35"/>
-      <c r="R82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" s="35" t="n">
+      <c r="R82" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T82" s="35"/>
-      <c r="U82" s="35"/>
+      <c r="U82" s="85"/>
       <c r="V82" s="36"/>
       <c r="W82" s="35"/>
       <c r="X82" s="36"/>
@@ -10856,7 +10910,7 @@
       <c r="F83" s="17" t="str">
         <v>jimeng-video-seedance-2.0-mini</v>
       </c>
-      <c r="G83" s="17" t="n">
+      <c r="G83" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="17" t="str">
@@ -10868,36 +10922,36 @@
       <c r="J83" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K83" s="20" t="n">
+      <c r="K83" s="71" t="n">
         <v>0.39</v>
       </c>
-      <c r="L83" s="17" t="n">
+      <c r="L83" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M83" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N83" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O83" s="21" t="n">
+      <c r="M83" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N83" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O83" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P83" s="23" t="n">
+      <c r="P83" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q83" s="17"/>
-      <c r="R83" s="17" t="n">
+      <c r="R83" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S83" s="17" t="n">
+      <c r="S83" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T83" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U83" s="17" t="n">
-        <v>46127</v>
+      <c r="U83" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V83" s="17" t="str">
         <v>不限</v>
@@ -10974,7 +11028,7 @@
       <c r="F84" s="17" t="str">
         <v>jimeng-video-seedance-2.0-fast-vip</v>
       </c>
-      <c r="G84" s="17" t="n">
+      <c r="G84" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H84" s="17" t="str">
@@ -10986,36 +11040,36 @@
       <c r="J84" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K84" s="20" t="n">
+      <c r="K84" s="71" t="n">
         <v>0.48</v>
       </c>
-      <c r="L84" s="17" t="n">
+      <c r="L84" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M84" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N84" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O84" s="21" t="n">
+      <c r="M84" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O84" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P84" s="23" t="n">
+      <c r="P84" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q84" s="17"/>
-      <c r="R84" s="17" t="n">
+      <c r="R84" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S84" s="17" t="n">
+      <c r="S84" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T84" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U84" s="17" t="n">
-        <v>46127</v>
+      <c r="U84" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V84" s="17" t="str">
         <v>不限</v>
@@ -11092,7 +11146,7 @@
       <c r="F85" s="17" t="str">
         <v>jimeng-video-seedance-2.0-vip</v>
       </c>
-      <c r="G85" s="17" t="n">
+      <c r="G85" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="17" t="str">
@@ -11104,36 +11158,36 @@
       <c r="J85" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K85" s="20" t="n">
+      <c r="K85" s="71" t="n">
         <v>0.62</v>
       </c>
-      <c r="L85" s="17" t="n">
+      <c r="L85" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M85" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N85" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O85" s="21" t="n">
+      <c r="M85" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N85" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P85" s="23" t="n">
+      <c r="P85" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q85" s="17"/>
-      <c r="R85" s="17" t="n">
+      <c r="R85" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S85" s="17" t="n">
+      <c r="S85" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T85" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U85" s="17" t="n">
-        <v>46127</v>
+      <c r="U85" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V85" s="17" t="str">
         <v>不限</v>
@@ -11208,7 +11262,7 @@
       <c r="F86" s="17" t="str">
         <v>jimeng-video-seedance-2.0-vip</v>
       </c>
-      <c r="G86" s="17" t="n">
+      <c r="G86" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="17" t="str">
@@ -11220,36 +11274,36 @@
       <c r="J86" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K86" s="20" t="n">
+      <c r="K86" s="71" t="n">
         <v>1.55</v>
       </c>
-      <c r="L86" s="17" t="n">
+      <c r="L86" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M86" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N86" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O86" s="21" t="n">
+      <c r="M86" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N86" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O86" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P86" s="23" t="n">
+      <c r="P86" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q86" s="17"/>
-      <c r="R86" s="17" t="n">
+      <c r="R86" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S86" s="17" t="n">
+      <c r="S86" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T86" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U86" s="17" t="n">
-        <v>46127</v>
+      <c r="U86" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V86" s="17" t="str">
         <v>不限</v>
@@ -11324,7 +11378,7 @@
       <c r="F87" s="17" t="str">
         <v>dimensio-seedance-2.0</v>
       </c>
-      <c r="G87" s="17" t="n">
+      <c r="G87" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="17" t="str">
@@ -11336,36 +11390,36 @@
       <c r="J87" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K87" s="20" t="n">
+      <c r="K87" s="71" t="n">
         <v>0.2</v>
       </c>
-      <c r="L87" s="17" t="n">
+      <c r="L87" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M87" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N87" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O87" s="21" t="n">
+      <c r="M87" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N87" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O87" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P87" s="23" t="n">
+      <c r="P87" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q87" s="17"/>
-      <c r="R87" s="17" t="n">
+      <c r="R87" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S87" s="17" t="n">
+      <c r="S87" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T87" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U87" s="17" t="n">
-        <v>46127</v>
+      <c r="U87" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V87" s="17" t="str">
         <v>不限</v>
@@ -11437,7 +11491,7 @@
       <c r="F88" s="17" t="str">
         <v>dimensio-seedance-2.0</v>
       </c>
-      <c r="G88" s="17" t="n">
+      <c r="G88" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="17" t="str">
@@ -11449,36 +11503,36 @@
       <c r="J88" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K88" s="20" t="n">
+      <c r="K88" s="71" t="n">
         <v>0.4</v>
       </c>
-      <c r="L88" s="17" t="n">
+      <c r="L88" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M88" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N88" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O88" s="21" t="n">
+      <c r="M88" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N88" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O88" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P88" s="23" t="n">
+      <c r="P88" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q88" s="17"/>
-      <c r="R88" s="17" t="n">
+      <c r="R88" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S88" s="17" t="n">
+      <c r="S88" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T88" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U88" s="17" t="n">
-        <v>46127</v>
+      <c r="U88" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V88" s="17" t="str">
         <v>不限</v>
@@ -11550,7 +11604,7 @@
       <c r="F89" s="17" t="str">
         <v>dimensio-seedance-2.0</v>
       </c>
-      <c r="G89" s="17" t="n">
+      <c r="G89" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H89" s="17" t="str">
@@ -11562,36 +11616,36 @@
       <c r="J89" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K89" s="20" t="n">
+      <c r="K89" s="71" t="n">
         <v>0.85</v>
       </c>
-      <c r="L89" s="17" t="n">
+      <c r="L89" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M89" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N89" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O89" s="21" t="n">
+      <c r="M89" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O89" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P89" s="23" t="n">
+      <c r="P89" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q89" s="17"/>
-      <c r="R89" s="17" t="n">
+      <c r="R89" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S89" s="17" t="n">
+      <c r="S89" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T89" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U89" s="17" t="n">
-        <v>46127</v>
+      <c r="U89" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V89" s="17" t="str">
         <v>不限</v>
@@ -11663,7 +11717,7 @@
       <c r="F90" s="17" t="str">
         <v>dimensio-seedance-2.0</v>
       </c>
-      <c r="G90" s="17" t="n">
+      <c r="G90" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="17" t="str">
@@ -11675,36 +11729,36 @@
       <c r="J90" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K90" s="20" t="n">
+      <c r="K90" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="L90" s="17" t="n">
+      <c r="L90" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M90" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N90" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O90" s="21" t="n">
+      <c r="M90" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N90" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O90" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P90" s="23" t="n">
+      <c r="P90" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q90" s="17"/>
-      <c r="R90" s="17" t="n">
+      <c r="R90" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S90" s="17" t="n">
+      <c r="S90" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T90" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U90" s="17" t="n">
-        <v>46127</v>
+      <c r="U90" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V90" s="17" t="str">
         <v>不限</v>
@@ -11776,7 +11830,7 @@
       <c r="F91" s="17" t="str">
         <v>dimensio-seedance-2.0-fast</v>
       </c>
-      <c r="G91" s="17" t="n">
+      <c r="G91" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="17" t="str">
@@ -11788,36 +11842,36 @@
       <c r="J91" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K91" s="20" t="n">
+      <c r="K91" s="71" t="n">
         <v>0.15</v>
       </c>
-      <c r="L91" s="17" t="n">
+      <c r="L91" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M91" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N91" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O91" s="21" t="n">
+      <c r="M91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N91" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P91" s="23" t="n">
+      <c r="P91" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q91" s="17"/>
-      <c r="R91" s="17" t="n">
+      <c r="R91" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S91" s="17" t="n">
+      <c r="S91" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T91" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U91" s="17" t="n">
-        <v>46127</v>
+      <c r="U91" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V91" s="17" t="str">
         <v>不限</v>
@@ -11889,7 +11943,7 @@
       <c r="F92" s="17" t="str">
         <v>dimensio-seedance-2.0-fast</v>
       </c>
-      <c r="G92" s="17" t="n">
+      <c r="G92" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H92" s="17" t="str">
@@ -11901,36 +11955,36 @@
       <c r="J92" s="20" t="str">
         <v>second</v>
       </c>
-      <c r="K92" s="20" t="n">
+      <c r="K92" s="71" t="n">
         <v>0.3</v>
       </c>
-      <c r="L92" s="17" t="n">
+      <c r="L92" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M92" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N92" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O92" s="21" t="n">
+      <c r="M92" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N92" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O92" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P92" s="23" t="n">
+      <c r="P92" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q92" s="17"/>
-      <c r="R92" s="17" t="n">
+      <c r="R92" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S92" s="17" t="n">
+      <c r="S92" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T92" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U92" s="17" t="n">
-        <v>46127</v>
+      <c r="U92" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V92" s="17" t="str">
         <v>不限</v>
@@ -11990,37 +12044,37 @@
       <c r="D93" s="35"/>
       <c r="E93" s="36"/>
       <c r="F93" s="35"/>
-      <c r="G93" s="36" t="n">
+      <c r="G93" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H93" s="17"/>
       <c r="I93" s="35"/>
       <c r="J93" s="35"/>
-      <c r="K93" s="35"/>
-      <c r="L93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" s="37" t="n">
+      <c r="K93" s="72"/>
+      <c r="L93" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q93" s="35"/>
-      <c r="R93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S93" s="35" t="n">
+      <c r="R93" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T93" s="35"/>
-      <c r="U93" s="35"/>
+      <c r="U93" s="85"/>
       <c r="V93" s="36"/>
       <c r="W93" s="35"/>
       <c r="X93" s="36"/>
@@ -12066,7 +12120,7 @@
       <c r="F94" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G94" s="17" t="n">
+      <c r="G94" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H94" s="17" t="str">
@@ -12078,36 +12132,36 @@
       <c r="J94" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K94" s="20" t="n">
+      <c r="K94" s="71" t="n">
         <v>4.9</v>
       </c>
-      <c r="L94" s="17" t="n">
+      <c r="L94" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M94" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N94" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O94" s="21" t="n">
+      <c r="M94" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N94" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P94" s="23" t="n">
+      <c r="P94" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q94" s="17"/>
-      <c r="R94" s="17" t="n">
+      <c r="R94" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S94" s="17" t="n">
+      <c r="S94" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T94" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U94" s="17" t="n">
-        <v>46127</v>
+      <c r="U94" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V94" s="17" t="str">
         <v>不限</v>
@@ -12177,7 +12231,7 @@
       <c r="F95" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G95" s="17" t="n">
+      <c r="G95" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H95" s="17" t="str">
@@ -12189,36 +12243,36 @@
       <c r="J95" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K95" s="20" t="n">
+      <c r="K95" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="L95" s="17" t="n">
+      <c r="L95" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M95" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N95" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O95" s="21" t="n">
+      <c r="M95" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N95" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O95" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P95" s="23" t="n">
+      <c r="P95" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q95" s="17"/>
-      <c r="R95" s="17" t="n">
+      <c r="R95" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S95" s="17" t="n">
+      <c r="S95" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T95" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U95" s="17" t="n">
-        <v>46127</v>
+      <c r="U95" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V95" s="17" t="str">
         <v>不限</v>
@@ -12281,7 +12335,7 @@
       <c r="F96" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G96" s="17" t="n">
+      <c r="G96" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H96" s="17" t="str">
@@ -12293,36 +12347,36 @@
       <c r="J96" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K96" s="20" t="n">
+      <c r="K96" s="71" t="n">
         <v>0.84</v>
       </c>
-      <c r="L96" s="17" t="n">
+      <c r="L96" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M96" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N96" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O96" s="21" t="n">
+      <c r="M96" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N96" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O96" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P96" s="23" t="n">
+      <c r="P96" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q96" s="17"/>
-      <c r="R96" s="17" t="n">
+      <c r="R96" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S96" s="17" t="n">
+      <c r="S96" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T96" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U96" s="17" t="n">
-        <v>46127</v>
+      <c r="U96" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V96" s="17" t="str">
         <v>不限</v>
@@ -12385,7 +12439,7 @@
       <c r="F97" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G97" s="17" t="n">
+      <c r="G97" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H97" s="17" t="str">
@@ -12397,36 +12451,36 @@
       <c r="J97" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K97" s="20" t="n">
+      <c r="K97" s="71" t="n">
         <v>1.68</v>
       </c>
-      <c r="L97" s="17" t="n">
+      <c r="L97" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M97" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N97" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O97" s="21" t="n">
+      <c r="M97" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N97" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O97" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P97" s="23" t="n">
+      <c r="P97" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q97" s="17"/>
-      <c r="R97" s="17" t="n">
+      <c r="R97" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S97" s="17" t="n">
+      <c r="S97" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T97" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U97" s="17" t="n">
-        <v>46127</v>
+      <c r="U97" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V97" s="17" t="str">
         <v>不限</v>
@@ -12489,7 +12543,7 @@
       <c r="F98" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G98" s="17" t="n">
+      <c r="G98" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H98" s="17" t="str">
@@ -12501,36 +12555,36 @@
       <c r="J98" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K98" s="20" t="n">
+      <c r="K98" s="71" t="n">
         <v>1.47</v>
       </c>
-      <c r="L98" s="17" t="n">
+      <c r="L98" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M98" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N98" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O98" s="21" t="n">
+      <c r="M98" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N98" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O98" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P98" s="23" t="n">
+      <c r="P98" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q98" s="17"/>
-      <c r="R98" s="17" t="n">
+      <c r="R98" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S98" s="17" t="n">
+      <c r="S98" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T98" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U98" s="17" t="n">
-        <v>46127</v>
+      <c r="U98" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V98" s="17" t="str">
         <v>不限</v>
@@ -12593,7 +12647,7 @@
       <c r="F99" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G99" s="17" t="n">
+      <c r="G99" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="17" t="str">
@@ -12605,36 +12659,36 @@
       <c r="J99" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K99" s="20" t="n">
+      <c r="K99" s="71" t="n">
         <v>2.1</v>
       </c>
-      <c r="L99" s="17" t="n">
+      <c r="L99" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M99" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N99" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O99" s="21" t="n">
+      <c r="M99" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N99" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O99" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P99" s="23" t="n">
+      <c r="P99" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q99" s="17"/>
-      <c r="R99" s="17" t="n">
+      <c r="R99" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S99" s="17" t="n">
+      <c r="S99" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T99" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U99" s="17" t="n">
-        <v>46127</v>
+      <c r="U99" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V99" s="17" t="str">
         <v>不限</v>
@@ -12697,7 +12751,7 @@
       <c r="F100" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G100" s="17" t="n">
+      <c r="G100" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="17" t="str">
@@ -12709,36 +12763,36 @@
       <c r="J100" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K100" s="20" t="n">
+      <c r="K100" s="71" t="n">
         <v>0.252</v>
       </c>
-      <c r="L100" s="17" t="n">
+      <c r="L100" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M100" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N100" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O100" s="21" t="n">
+      <c r="M100" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N100" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O100" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P100" s="23" t="n">
+      <c r="P100" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q100" s="17"/>
-      <c r="R100" s="17" t="n">
+      <c r="R100" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S100" s="17" t="n">
+      <c r="S100" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T100" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U100" s="17" t="n">
-        <v>46127</v>
+      <c r="U100" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V100" s="17" t="str">
         <v>不限</v>
@@ -12801,7 +12855,7 @@
       <c r="F101" s="17" t="str">
         <v>videos-standard</v>
       </c>
-      <c r="G101" s="17" t="n">
+      <c r="G101" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="17" t="str">
@@ -12813,36 +12867,36 @@
       <c r="J101" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K101" s="20" t="n">
+      <c r="K101" s="71" t="n">
         <v>0.504</v>
       </c>
-      <c r="L101" s="17" t="n">
+      <c r="L101" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M101" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N101" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O101" s="21" t="n">
+      <c r="M101" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N101" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O101" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P101" s="23" t="n">
+      <c r="P101" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q101" s="17"/>
-      <c r="R101" s="17" t="n">
+      <c r="R101" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S101" s="17" t="n">
+      <c r="S101" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T101" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U101" s="17" t="n">
-        <v>46127</v>
+      <c r="U101" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V101" s="17" t="str">
         <v>不限</v>
@@ -12905,7 +12959,7 @@
       <c r="F102" s="17" t="str">
         <v>videos-fast</v>
       </c>
-      <c r="G102" s="17" t="n">
+      <c r="G102" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H102" s="17" t="str">
@@ -12917,36 +12971,36 @@
       <c r="J102" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K102" s="20" t="n">
+      <c r="K102" s="71" t="n">
         <v>2.8</v>
       </c>
-      <c r="L102" s="17" t="n">
+      <c r="L102" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M102" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N102" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O102" s="21" t="n">
+      <c r="M102" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N102" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O102" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P102" s="23" t="n">
+      <c r="P102" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q102" s="17"/>
-      <c r="R102" s="17" t="n">
+      <c r="R102" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S102" s="17" t="n">
+      <c r="S102" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T102" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U102" s="17" t="n">
-        <v>46127</v>
+      <c r="U102" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V102" s="17" t="str">
         <v>不限</v>
@@ -13009,7 +13063,7 @@
       <c r="F103" s="17" t="str">
         <v>videos-fast</v>
       </c>
-      <c r="G103" s="17" t="n">
+      <c r="G103" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H103" s="17" t="str">
@@ -13021,36 +13075,36 @@
       <c r="J103" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K103" s="20" t="n">
+      <c r="K103" s="71" t="n">
         <v>4.9</v>
       </c>
-      <c r="L103" s="17" t="n">
+      <c r="L103" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M103" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N103" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O103" s="21" t="n">
+      <c r="M103" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N103" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O103" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P103" s="23" t="n">
+      <c r="P103" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q103" s="17"/>
-      <c r="R103" s="17" t="n">
+      <c r="R103" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S103" s="17" t="n">
+      <c r="S103" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T103" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U103" s="17" t="n">
-        <v>46127</v>
+      <c r="U103" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V103" s="17" t="str">
         <v>不限</v>
@@ -13113,7 +13167,7 @@
       <c r="F104" s="17" t="str">
         <v>videos-fast</v>
       </c>
-      <c r="G104" s="17" t="n">
+      <c r="G104" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H104" s="17" t="str">
@@ -13125,36 +13179,36 @@
       <c r="J104" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K104" s="20" t="n">
+      <c r="K104" s="71" t="n">
         <v>0.84</v>
       </c>
-      <c r="L104" s="17" t="n">
+      <c r="L104" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M104" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N104" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O104" s="21" t="n">
+      <c r="M104" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N104" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O104" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P104" s="23" t="n">
+      <c r="P104" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q104" s="17"/>
-      <c r="R104" s="17" t="n">
+      <c r="R104" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S104" s="17" t="n">
+      <c r="S104" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T104" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U104" s="17" t="n">
-        <v>46127</v>
+      <c r="U104" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V104" s="17" t="str">
         <v>不限</v>
@@ -13217,7 +13271,7 @@
       <c r="F105" s="17" t="str">
         <v>videos-fast</v>
       </c>
-      <c r="G105" s="17" t="n">
+      <c r="G105" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H105" s="17" t="str">
@@ -13229,36 +13283,36 @@
       <c r="J105" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K105" s="20" t="n">
+      <c r="K105" s="71" t="n">
         <v>1.47</v>
       </c>
-      <c r="L105" s="17" t="n">
+      <c r="L105" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M105" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N105" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O105" s="21" t="n">
+      <c r="M105" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N105" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O105" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P105" s="23" t="n">
+      <c r="P105" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q105" s="17"/>
-      <c r="R105" s="17" t="n">
+      <c r="R105" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S105" s="17" t="n">
+      <c r="S105" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T105" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U105" s="17" t="n">
-        <v>46127</v>
+      <c r="U105" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V105" s="17" t="str">
         <v>不限</v>
@@ -13321,7 +13375,7 @@
       <c r="F106" s="44" t="str">
         <v>videos-mini</v>
       </c>
-      <c r="G106" s="44" t="n">
+      <c r="G106" s="69" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="17" t="str">
@@ -13333,36 +13387,36 @@
       <c r="J106" s="46" t="str">
         <v>call</v>
       </c>
-      <c r="K106" s="47" t="n">
+      <c r="K106" s="73" t="n">
         <v>2.1</v>
       </c>
-      <c r="L106" s="43" t="n">
+      <c r="L106" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="M106" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N106" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="O106" s="49" t="n">
+      <c r="M106" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N106" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O106" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="P106" s="50" t="n">
+      <c r="P106" s="80" t="n">
         <v>3</v>
       </c>
       <c r="Q106" s="48"/>
-      <c r="R106" s="48" t="n">
+      <c r="R106" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="S106" s="48" t="n">
+      <c r="S106" s="79" t="n">
         <v>0</v>
       </c>
       <c r="T106" s="48" t="str">
         <v>否</v>
       </c>
-      <c r="U106" s="42" t="n">
-        <v>46127</v>
+      <c r="U106" s="86" t="str">
+        <v>4-15</v>
       </c>
       <c r="V106" s="45" t="str">
         <v>不限</v>
@@ -13432,7 +13486,7 @@
       <c r="F107" s="44" t="str">
         <v>videos-mini</v>
       </c>
-      <c r="G107" s="44" t="n">
+      <c r="G107" s="69" t="n">
         <v>2</v>
       </c>
       <c r="H107" s="17" t="str">
@@ -13444,36 +13498,36 @@
       <c r="J107" s="46" t="str">
         <v>call</v>
       </c>
-      <c r="K107" s="47" t="n">
+      <c r="K107" s="73" t="n">
         <v>3.5</v>
       </c>
-      <c r="L107" s="43" t="n">
+      <c r="L107" s="78" t="n">
         <v>9</v>
       </c>
-      <c r="M107" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="N107" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="O107" s="49" t="n">
+      <c r="M107" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N107" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="O107" s="78" t="n">
         <v>15</v>
       </c>
-      <c r="P107" s="50" t="n">
+      <c r="P107" s="80" t="n">
         <v>3</v>
       </c>
       <c r="Q107" s="48"/>
-      <c r="R107" s="48" t="n">
+      <c r="R107" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="S107" s="48" t="n">
+      <c r="S107" s="79" t="n">
         <v>0</v>
       </c>
       <c r="T107" s="48" t="str">
         <v>否</v>
       </c>
-      <c r="U107" s="42" t="n">
-        <v>46127</v>
+      <c r="U107" s="86" t="str">
+        <v>4-15</v>
       </c>
       <c r="V107" s="45" t="str">
         <v>不限</v>
@@ -13543,7 +13597,7 @@
       <c r="F108" s="17" t="str">
         <v>videos-4-720p</v>
       </c>
-      <c r="G108" s="17" t="n">
+      <c r="G108" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="17" t="str">
@@ -13555,36 +13609,36 @@
       <c r="J108" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K108" s="20" t="n">
+      <c r="K108" s="71" t="n">
         <v>0.33</v>
       </c>
-      <c r="L108" s="17" t="n">
+      <c r="L108" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M108" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N108" s="17" t="n">
+      <c r="M108" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N108" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O108" s="21" t="n">
+      <c r="O108" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P108" s="23" t="n">
+      <c r="P108" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q108" s="17"/>
-      <c r="R108" s="17" t="n">
+      <c r="R108" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S108" s="17" t="n">
+      <c r="S108" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T108" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U108" s="17" t="n">
-        <v>46127</v>
+      <c r="U108" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V108" s="17" t="str">
         <v>不限</v>
@@ -13645,7 +13699,7 @@
       <c r="F109" s="17" t="str">
         <v>videos-4-480p</v>
       </c>
-      <c r="G109" s="17" t="n">
+      <c r="G109" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H109" s="17" t="str">
@@ -13657,36 +13711,36 @@
       <c r="J109" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K109" s="20" t="n">
+      <c r="K109" s="71" t="n">
         <v>0.23</v>
       </c>
-      <c r="L109" s="17" t="n">
+      <c r="L109" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M109" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N109" s="17" t="n">
+      <c r="M109" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N109" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O109" s="21" t="n">
+      <c r="O109" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P109" s="23" t="n">
+      <c r="P109" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q109" s="17"/>
-      <c r="R109" s="17" t="n">
+      <c r="R109" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S109" s="17" t="n">
+      <c r="S109" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T109" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U109" s="17" t="n">
-        <v>46127</v>
+      <c r="U109" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V109" s="17" t="str">
         <v>不限</v>
@@ -13747,7 +13801,7 @@
       <c r="F110" s="17" t="str">
         <v>videos-4-720p</v>
       </c>
-      <c r="G110" s="17" t="n">
+      <c r="G110" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H110" s="17" t="str">
@@ -13759,36 +13813,36 @@
       <c r="J110" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K110" s="20" t="n">
+      <c r="K110" s="71" t="n">
         <v>0.33</v>
       </c>
-      <c r="L110" s="17" t="n">
+      <c r="L110" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M110" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N110" s="17" t="n">
+      <c r="M110" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N110" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O110" s="21" t="n">
+      <c r="O110" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P110" s="23" t="n">
+      <c r="P110" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q110" s="17"/>
-      <c r="R110" s="17" t="n">
+      <c r="R110" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S110" s="17" t="n">
+      <c r="S110" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T110" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U110" s="17" t="n">
-        <v>46127</v>
+      <c r="U110" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V110" s="17" t="str">
         <v>不限</v>
@@ -13849,7 +13903,7 @@
       <c r="F111" s="17" t="str">
         <v>videos-4-fast-480p</v>
       </c>
-      <c r="G111" s="17" t="n">
+      <c r="G111" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H111" s="17" t="str">
@@ -13861,36 +13915,36 @@
       <c r="J111" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K111" s="20" t="n">
+      <c r="K111" s="71" t="n">
         <v>0.13</v>
       </c>
-      <c r="L111" s="17" t="n">
+      <c r="L111" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M111" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N111" s="17" t="n">
+      <c r="M111" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N111" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O111" s="21" t="n">
+      <c r="O111" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P111" s="23" t="n">
+      <c r="P111" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q111" s="17"/>
-      <c r="R111" s="17" t="n">
+      <c r="R111" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S111" s="17" t="n">
+      <c r="S111" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T111" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U111" s="17" t="n">
-        <v>46127</v>
+      <c r="U111" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V111" s="17" t="str">
         <v>不限</v>
@@ -13951,7 +14005,7 @@
       <c r="F112" s="17" t="str">
         <v>videos-4-fast-720p</v>
       </c>
-      <c r="G112" s="17" t="n">
+      <c r="G112" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H112" s="17" t="str">
@@ -13963,36 +14017,36 @@
       <c r="J112" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K112" s="20" t="n">
+      <c r="K112" s="71" t="n">
         <v>0.23</v>
       </c>
-      <c r="L112" s="17" t="n">
+      <c r="L112" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M112" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N112" s="17" t="n">
+      <c r="M112" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N112" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O112" s="21" t="n">
+      <c r="O112" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P112" s="23" t="n">
+      <c r="P112" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q112" s="17"/>
-      <c r="R112" s="17" t="n">
+      <c r="R112" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S112" s="17" t="n">
+      <c r="S112" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T112" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U112" s="17" t="n">
-        <v>46127</v>
+      <c r="U112" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V112" s="17" t="str">
         <v>不限</v>
@@ -14053,7 +14107,7 @@
       <c r="F113" s="17" t="str">
         <v>videos-4-mini-480p</v>
       </c>
-      <c r="G113" s="17" t="n">
+      <c r="G113" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H113" s="17" t="str">
@@ -14065,36 +14119,36 @@
       <c r="J113" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K113" s="20" t="n">
+      <c r="K113" s="71" t="n">
         <v>0.09</v>
       </c>
-      <c r="L113" s="17" t="n">
+      <c r="L113" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M113" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N113" s="17" t="n">
+      <c r="M113" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N113" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O113" s="21" t="n">
+      <c r="O113" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P113" s="23" t="n">
+      <c r="P113" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q113" s="17"/>
-      <c r="R113" s="17" t="n">
+      <c r="R113" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S113" s="17" t="n">
+      <c r="S113" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T113" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U113" s="17" t="n">
-        <v>46127</v>
+      <c r="U113" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V113" s="17" t="str">
         <v>不限</v>
@@ -14155,7 +14209,7 @@
       <c r="F114" s="17" t="str">
         <v>videos-4-mini-720p</v>
       </c>
-      <c r="G114" s="17" t="n">
+      <c r="G114" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H114" s="17" t="str">
@@ -14167,36 +14221,36 @@
       <c r="J114" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K114" s="20" t="n">
+      <c r="K114" s="71" t="n">
         <v>0.16</v>
       </c>
-      <c r="L114" s="17" t="n">
+      <c r="L114" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M114" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N114" s="17" t="n">
+      <c r="M114" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N114" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O114" s="21" t="n">
+      <c r="O114" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P114" s="23" t="n">
+      <c r="P114" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q114" s="17"/>
-      <c r="R114" s="17" t="n">
+      <c r="R114" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S114" s="17" t="n">
+      <c r="S114" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T114" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U114" s="17" t="n">
-        <v>46127</v>
+      <c r="U114" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V114" s="17" t="str">
         <v>不限</v>
@@ -14245,37 +14299,37 @@
       <c r="D115" s="35"/>
       <c r="E115" s="36"/>
       <c r="F115" s="35"/>
-      <c r="G115" s="36" t="n">
+      <c r="G115" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H115" s="17"/>
       <c r="I115" s="35"/>
       <c r="J115" s="35"/>
-      <c r="K115" s="35"/>
-      <c r="L115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" s="37" t="n">
+      <c r="K115" s="72"/>
+      <c r="L115" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q115" s="35"/>
-      <c r="R115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" s="35" t="n">
+      <c r="R115" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T115" s="35"/>
-      <c r="U115" s="35"/>
+      <c r="U115" s="85"/>
       <c r="V115" s="36"/>
       <c r="W115" s="35"/>
       <c r="X115" s="36"/>
@@ -14321,7 +14375,7 @@
       <c r="F116" s="17" t="str">
         <v>4sdance_fast431</v>
       </c>
-      <c r="G116" s="17" t="n">
+      <c r="G116" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H116" s="17" t="str">
@@ -14333,36 +14387,36 @@
       <c r="J116" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K116" s="20" t="n">
+      <c r="K116" s="71" t="n">
         <v>3.35</v>
       </c>
-      <c r="L116" s="17" t="n">
+      <c r="L116" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M116" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N116" s="17" t="n">
+      <c r="M116" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N116" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O116" s="21" t="n">
+      <c r="O116" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P116" s="23" t="n">
+      <c r="P116" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q116" s="17"/>
-      <c r="R116" s="17" t="n">
+      <c r="R116" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S116" s="17" t="n">
+      <c r="S116" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T116" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U116" s="17" t="n">
-        <v>46127</v>
+      <c r="U116" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V116" s="17" t="str">
         <v>不限</v>
@@ -14425,7 +14479,7 @@
       <c r="F117" s="17" t="str">
         <v>4sdance_fast431</v>
       </c>
-      <c r="G117" s="17" t="n">
+      <c r="G117" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H117" s="17" t="str">
@@ -14437,36 +14491,36 @@
       <c r="J117" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K117" s="20" t="n">
+      <c r="K117" s="71" t="n">
         <v>7.2</v>
       </c>
-      <c r="L117" s="17" t="n">
+      <c r="L117" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M117" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N117" s="17" t="n">
+      <c r="M117" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N117" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O117" s="21" t="n">
+      <c r="O117" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P117" s="23" t="n">
+      <c r="P117" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q117" s="17"/>
-      <c r="R117" s="17" t="n">
+      <c r="R117" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S117" s="17" t="n">
+      <c r="S117" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T117" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U117" s="17" t="n">
-        <v>46127</v>
+      <c r="U117" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V117" s="17" t="str">
         <v>不限</v>
@@ -14529,7 +14583,7 @@
       <c r="F118" s="55" t="str">
         <v>4sdance_fast431</v>
       </c>
-      <c r="G118" s="42" t="n">
+      <c r="G118" s="69" t="n">
         <v>2</v>
       </c>
       <c r="H118" s="42" t="str">
@@ -14541,36 +14595,36 @@
       <c r="J118" s="46" t="str">
         <v>call</v>
       </c>
-      <c r="K118" s="58" t="n">
+      <c r="K118" s="74" t="n">
         <v>7.2</v>
       </c>
-      <c r="L118" s="17" t="n">
+      <c r="L118" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M118" s="59" t="n">
-        <v>3</v>
-      </c>
-      <c r="N118" s="60" t="n">
+      <c r="M118" s="79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N118" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="O118" s="61" t="n">
+      <c r="O118" s="81" t="n">
         <v>8</v>
       </c>
-      <c r="P118" s="62" t="n">
+      <c r="P118" s="82" t="n">
         <v>3</v>
       </c>
       <c r="Q118" s="63"/>
-      <c r="R118" s="63" t="n">
+      <c r="R118" s="79" t="n">
         <v>15</v>
       </c>
-      <c r="S118" s="63" t="n">
+      <c r="S118" s="79" t="n">
         <v>0</v>
       </c>
       <c r="T118" s="63" t="str">
         <v>否</v>
       </c>
-      <c r="U118" s="64" t="n">
-        <v>46127</v>
+      <c r="U118" s="87" t="str">
+        <v>4-15</v>
       </c>
       <c r="V118" s="65" t="str">
         <v>不限</v>
@@ -14640,7 +14694,7 @@
       <c r="F119" s="17" t="str">
         <v>4sdance431</v>
       </c>
-      <c r="G119" s="17" t="n">
+      <c r="G119" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H119" s="17" t="str">
@@ -14652,36 +14706,36 @@
       <c r="J119" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K119" s="20" t="n">
+      <c r="K119" s="71" t="n">
         <v>4.1</v>
       </c>
-      <c r="L119" s="17" t="n">
+      <c r="L119" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M119" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N119" s="17" t="n">
+      <c r="M119" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N119" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O119" s="21" t="n">
+      <c r="O119" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P119" s="23" t="n">
+      <c r="P119" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q119" s="17"/>
-      <c r="R119" s="17" t="n">
+      <c r="R119" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S119" s="17" t="n">
+      <c r="S119" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T119" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U119" s="17" t="n">
-        <v>46127</v>
+      <c r="U119" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V119" s="17" t="str">
         <v>不限</v>
@@ -14744,7 +14798,7 @@
       <c r="F120" s="17" t="str">
         <v>4sdance431</v>
       </c>
-      <c r="G120" s="17" t="n">
+      <c r="G120" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H120" s="17" t="str">
@@ -14756,36 +14810,36 @@
       <c r="J120" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K120" s="20" t="n">
+      <c r="K120" s="71" t="n">
         <v>8.9</v>
       </c>
-      <c r="L120" s="17" t="n">
+      <c r="L120" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M120" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N120" s="17" t="n">
+      <c r="M120" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N120" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O120" s="21" t="n">
+      <c r="O120" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P120" s="23" t="n">
+      <c r="P120" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q120" s="17"/>
-      <c r="R120" s="17" t="n">
+      <c r="R120" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S120" s="17" t="n">
+      <c r="S120" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T120" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U120" s="17" t="n">
-        <v>46127</v>
+      <c r="U120" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V120" s="17" t="str">
         <v>不限</v>
@@ -14848,7 +14902,7 @@
       <c r="F121" s="17" t="str">
         <v>4sdance_v2.0_900</v>
       </c>
-      <c r="G121" s="17" t="n">
+      <c r="G121" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H121" s="17" t="str">
@@ -14860,36 +14914,36 @@
       <c r="J121" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K121" s="20" t="n">
+      <c r="K121" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="L121" s="17" t="n">
+      <c r="L121" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M121" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" s="21" t="n">
+      <c r="M121" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="P121" s="23" t="n">
+      <c r="P121" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q121" s="17"/>
-      <c r="R121" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="17" t="n">
+      <c r="R121" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T121" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U121" s="17" t="n">
-        <v>46127</v>
+      <c r="U121" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V121" s="17" t="str">
         <v>不限</v>
@@ -14952,7 +15006,7 @@
       <c r="F122" s="17" t="str">
         <v>4sdance933_fast</v>
       </c>
-      <c r="G122" s="17" t="n">
+      <c r="G122" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H122" s="17" t="str">
@@ -14964,36 +15018,36 @@
       <c r="J122" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K122" s="20" t="n">
+      <c r="K122" s="71" t="n">
         <v>0.48</v>
       </c>
-      <c r="L122" s="17" t="n">
+      <c r="L122" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M122" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N122" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O122" s="21" t="n">
+      <c r="M122" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O122" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P122" s="23" t="n">
+      <c r="P122" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q122" s="17"/>
-      <c r="R122" s="17" t="n">
+      <c r="R122" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S122" s="17" t="n">
+      <c r="S122" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T122" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U122" s="17" t="n">
-        <v>46127</v>
+      <c r="U122" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V122" s="17" t="str">
         <v>不限</v>
@@ -15056,7 +15110,7 @@
       <c r="F123" s="17" t="str">
         <v>4sdance_fast_933face</v>
       </c>
-      <c r="G123" s="17" t="n">
+      <c r="G123" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H123" s="17" t="str">
@@ -15068,36 +15122,36 @@
       <c r="J123" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K123" s="20" t="n">
+      <c r="K123" s="71" t="n">
         <v>0.48</v>
       </c>
-      <c r="L123" s="17" t="n">
+      <c r="L123" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M123" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N123" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O123" s="21" t="n">
+      <c r="M123" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N123" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O123" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P123" s="23" t="n">
+      <c r="P123" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q123" s="17"/>
-      <c r="R123" s="17" t="n">
+      <c r="R123" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S123" s="17" t="n">
+      <c r="S123" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T123" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U123" s="17" t="n">
-        <v>46127</v>
+      <c r="U123" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V123" s="17" t="str">
         <v>不限</v>
@@ -15160,7 +15214,7 @@
       <c r="F124" s="17" t="str">
         <v>4sdance933</v>
       </c>
-      <c r="G124" s="17" t="n">
+      <c r="G124" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H124" s="17" t="str">
@@ -15172,36 +15226,36 @@
       <c r="J124" s="17" t="str">
         <v>second</v>
       </c>
-      <c r="K124" s="20" t="n">
+      <c r="K124" s="71" t="n">
         <v>0.6</v>
       </c>
-      <c r="L124" s="17" t="n">
+      <c r="L124" s="76" t="n">
         <v>9</v>
       </c>
-      <c r="M124" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N124" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O124" s="21" t="n">
+      <c r="M124" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N124" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="O124" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="P124" s="23" t="n">
+      <c r="P124" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q124" s="17"/>
-      <c r="R124" s="17" t="n">
+      <c r="R124" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S124" s="17" t="n">
+      <c r="S124" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T124" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U124" s="17" t="n">
-        <v>46127</v>
+      <c r="U124" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V124" s="17" t="str">
         <v>不限</v>
@@ -15264,7 +15318,7 @@
       <c r="F125" s="17" t="str">
         <v>4sdance_431_480p</v>
       </c>
-      <c r="G125" s="17" t="n">
+      <c r="G125" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H125" s="17" t="str">
@@ -15276,36 +15330,36 @@
       <c r="J125" s="17" t="str">
         <v>call</v>
       </c>
-      <c r="K125" s="20" t="n">
+      <c r="K125" s="71" t="n">
         <v>4.1</v>
       </c>
-      <c r="L125" s="17" t="n">
+      <c r="L125" s="76" t="n">
         <v>4</v>
       </c>
-      <c r="M125" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N125" s="17" t="n">
+      <c r="M125" s="76" t="n">
+        <v>3</v>
+      </c>
+      <c r="N125" s="76" t="n">
         <v>1</v>
       </c>
-      <c r="O125" s="21" t="n">
+      <c r="O125" s="76" t="n">
         <v>8</v>
       </c>
-      <c r="P125" s="23" t="n">
+      <c r="P125" s="76" t="n">
         <v>3</v>
       </c>
       <c r="Q125" s="17"/>
-      <c r="R125" s="17" t="n">
+      <c r="R125" s="76" t="n">
         <v>15</v>
       </c>
-      <c r="S125" s="17" t="n">
+      <c r="S125" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T125" s="17" t="str">
         <v>否</v>
       </c>
-      <c r="U125" s="17" t="n">
-        <v>46127</v>
+      <c r="U125" s="84" t="str">
+        <v>4-15</v>
       </c>
       <c r="V125" s="17" t="str">
         <v>不限</v>
@@ -15356,37 +15410,37 @@
       <c r="D126" s="35"/>
       <c r="E126" s="36"/>
       <c r="F126" s="35"/>
-      <c r="G126" s="36" t="n">
+      <c r="G126" s="68" t="n">
         <v>2</v>
       </c>
       <c r="H126" s="36"/>
       <c r="I126" s="35"/>
       <c r="J126" s="35"/>
-      <c r="K126" s="35"/>
-      <c r="L126" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" s="37" t="n">
+      <c r="K126" s="72"/>
+      <c r="L126" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" s="77" t="n">
         <v>0</v>
       </c>
       <c r="Q126" s="35"/>
-      <c r="R126" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" s="35" t="n">
+      <c r="R126" s="77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" s="77" t="n">
         <v>0</v>
       </c>
       <c r="T126" s="35"/>
-      <c r="U126" s="35"/>
+      <c r="U126" s="85"/>
       <c r="V126" s="36"/>
       <c r="W126" s="35"/>
       <c r="X126" s="36">
@@ -15436,37 +15490,37 @@
       <c r="D127" s="20"/>
       <c r="E127" s="17"/>
       <c r="F127" s="20"/>
-      <c r="G127" s="17" t="n">
+      <c r="G127" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H127" s="17"/>
       <c r="I127" s="20"/>
       <c r="J127" s="20"/>
-      <c r="K127" s="20"/>
-      <c r="L127" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N127" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" s="23" t="n">
+      <c r="K127" s="71"/>
+      <c r="L127" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q127" s="20"/>
-      <c r="R127" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" s="20" t="n">
+      <c r="R127" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T127" s="20"/>
-      <c r="U127" s="20"/>
+      <c r="U127" s="84"/>
       <c r="V127" s="17"/>
       <c r="W127" s="20"/>
       <c r="X127" s="17">
@@ -15509,37 +15563,37 @@
       <c r="D128" s="20"/>
       <c r="E128" s="17"/>
       <c r="F128" s="20"/>
-      <c r="G128" s="17" t="n">
+      <c r="G128" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H128" s="17"/>
       <c r="I128" s="20"/>
       <c r="J128" s="20"/>
-      <c r="K128" s="20"/>
-      <c r="L128" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" s="23" t="n">
+      <c r="K128" s="71"/>
+      <c r="L128" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q128" s="20"/>
-      <c r="R128" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" s="20" t="n">
+      <c r="R128" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T128" s="20"/>
-      <c r="U128" s="20"/>
+      <c r="U128" s="84"/>
       <c r="V128" s="17"/>
       <c r="W128" s="20"/>
       <c r="X128" s="17">
@@ -15582,37 +15636,37 @@
       <c r="D129" s="20"/>
       <c r="E129" s="17"/>
       <c r="F129" s="20"/>
-      <c r="G129" s="17" t="n">
+      <c r="G129" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H129" s="17"/>
       <c r="I129" s="20"/>
       <c r="J129" s="20"/>
-      <c r="K129" s="20"/>
-      <c r="L129" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" s="23" t="n">
+      <c r="K129" s="71"/>
+      <c r="L129" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q129" s="20"/>
-      <c r="R129" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" s="20" t="n">
+      <c r="R129" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T129" s="20"/>
-      <c r="U129" s="20"/>
+      <c r="U129" s="84"/>
       <c r="V129" s="17"/>
       <c r="W129" s="20"/>
       <c r="X129" s="17">
@@ -15655,37 +15709,37 @@
       <c r="D130" s="20"/>
       <c r="E130" s="17"/>
       <c r="F130" s="20"/>
-      <c r="G130" s="17" t="n">
+      <c r="G130" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H130" s="17"/>
       <c r="I130" s="20"/>
       <c r="J130" s="20"/>
-      <c r="K130" s="20"/>
-      <c r="L130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N130" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" s="23" t="n">
+      <c r="K130" s="71"/>
+      <c r="L130" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q130" s="20"/>
-      <c r="R130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" s="20" t="n">
+      <c r="R130" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T130" s="20"/>
-      <c r="U130" s="20"/>
+      <c r="U130" s="84"/>
       <c r="V130" s="17"/>
       <c r="W130" s="20"/>
       <c r="X130" s="17">
@@ -15728,37 +15782,37 @@
       <c r="D131" s="20"/>
       <c r="E131" s="17"/>
       <c r="F131" s="20"/>
-      <c r="G131" s="17" t="n">
+      <c r="G131" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H131" s="17"/>
       <c r="I131" s="20"/>
       <c r="J131" s="20"/>
-      <c r="K131" s="20"/>
-      <c r="L131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N131" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" s="23" t="n">
+      <c r="K131" s="71"/>
+      <c r="L131" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q131" s="20"/>
-      <c r="R131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" s="20" t="n">
+      <c r="R131" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T131" s="20"/>
-      <c r="U131" s="20"/>
+      <c r="U131" s="84"/>
       <c r="V131" s="17"/>
       <c r="W131" s="20"/>
       <c r="X131" s="17">
@@ -15801,37 +15855,37 @@
       <c r="D132" s="20"/>
       <c r="E132" s="17"/>
       <c r="F132" s="20"/>
-      <c r="G132" s="17" t="n">
+      <c r="G132" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="17"/>
       <c r="I132" s="20"/>
       <c r="J132" s="20"/>
-      <c r="K132" s="20"/>
-      <c r="L132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" s="23" t="n">
+      <c r="K132" s="71"/>
+      <c r="L132" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q132" s="20"/>
-      <c r="R132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" s="20" t="n">
+      <c r="R132" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T132" s="20"/>
-      <c r="U132" s="20"/>
+      <c r="U132" s="84"/>
       <c r="V132" s="17"/>
       <c r="W132" s="20"/>
       <c r="X132" s="17">
@@ -15874,37 +15928,37 @@
       <c r="D133" s="20"/>
       <c r="E133" s="17"/>
       <c r="F133" s="20"/>
-      <c r="G133" s="17" t="n">
+      <c r="G133" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H133" s="17"/>
       <c r="I133" s="20"/>
       <c r="J133" s="20"/>
-      <c r="K133" s="20"/>
-      <c r="L133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" s="23" t="n">
+      <c r="K133" s="71"/>
+      <c r="L133" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q133" s="20"/>
-      <c r="R133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" s="20" t="n">
+      <c r="R133" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T133" s="20"/>
-      <c r="U133" s="20"/>
+      <c r="U133" s="84"/>
       <c r="V133" s="17"/>
       <c r="W133" s="20"/>
       <c r="X133" s="17">
@@ -15947,37 +16001,37 @@
       <c r="D134" s="20"/>
       <c r="E134" s="17"/>
       <c r="F134" s="20"/>
-      <c r="G134" s="17" t="n">
+      <c r="G134" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H134" s="17"/>
       <c r="I134" s="20"/>
       <c r="J134" s="20"/>
-      <c r="K134" s="20"/>
-      <c r="L134" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" s="23" t="n">
+      <c r="K134" s="71"/>
+      <c r="L134" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q134" s="20"/>
-      <c r="R134" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" s="20" t="n">
+      <c r="R134" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T134" s="20"/>
-      <c r="U134" s="20"/>
+      <c r="U134" s="84"/>
       <c r="V134" s="17"/>
       <c r="W134" s="20"/>
       <c r="X134" s="17">
@@ -16020,37 +16074,37 @@
       <c r="D135" s="20"/>
       <c r="E135" s="17"/>
       <c r="F135" s="20"/>
-      <c r="G135" s="17" t="n">
+      <c r="G135" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H135" s="17"/>
       <c r="I135" s="20"/>
       <c r="J135" s="20"/>
-      <c r="K135" s="20"/>
-      <c r="L135" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" s="23" t="n">
+      <c r="K135" s="71"/>
+      <c r="L135" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q135" s="20"/>
-      <c r="R135" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" s="20" t="n">
+      <c r="R135" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T135" s="20"/>
-      <c r="U135" s="20"/>
+      <c r="U135" s="84"/>
       <c r="V135" s="17"/>
       <c r="W135" s="20"/>
       <c r="X135" s="17">
@@ -16093,37 +16147,37 @@
       <c r="D136" s="20"/>
       <c r="E136" s="17"/>
       <c r="F136" s="20"/>
-      <c r="G136" s="17" t="n">
+      <c r="G136" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H136" s="17"/>
       <c r="I136" s="20"/>
       <c r="J136" s="20"/>
-      <c r="K136" s="20"/>
-      <c r="L136" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O136" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P136" s="23" t="n">
+      <c r="K136" s="71"/>
+      <c r="L136" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P136" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q136" s="20"/>
-      <c r="R136" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" s="20" t="n">
+      <c r="R136" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T136" s="20"/>
-      <c r="U136" s="20"/>
+      <c r="U136" s="84"/>
       <c r="V136" s="17"/>
       <c r="W136" s="20"/>
       <c r="X136" s="17">
@@ -16166,37 +16220,37 @@
       <c r="D137" s="20"/>
       <c r="E137" s="17"/>
       <c r="F137" s="20"/>
-      <c r="G137" s="17" t="n">
+      <c r="G137" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H137" s="17"/>
       <c r="I137" s="20"/>
       <c r="J137" s="20"/>
-      <c r="K137" s="20"/>
-      <c r="L137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N137" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P137" s="23" t="n">
+      <c r="K137" s="71"/>
+      <c r="L137" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P137" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q137" s="20"/>
-      <c r="R137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S137" s="20" t="n">
+      <c r="R137" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T137" s="20"/>
-      <c r="U137" s="20"/>
+      <c r="U137" s="84"/>
       <c r="V137" s="17"/>
       <c r="W137" s="20"/>
       <c r="X137" s="17">
@@ -16239,37 +16293,37 @@
       <c r="D138" s="20"/>
       <c r="E138" s="17"/>
       <c r="F138" s="20"/>
-      <c r="G138" s="17" t="n">
+      <c r="G138" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H138" s="17"/>
       <c r="I138" s="20"/>
       <c r="J138" s="20"/>
-      <c r="K138" s="20"/>
-      <c r="L138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N138" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P138" s="23" t="n">
+      <c r="K138" s="71"/>
+      <c r="L138" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P138" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q138" s="20"/>
-      <c r="R138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S138" s="20" t="n">
+      <c r="R138" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T138" s="20"/>
-      <c r="U138" s="20"/>
+      <c r="U138" s="84"/>
       <c r="V138" s="17"/>
       <c r="W138" s="20"/>
       <c r="X138" s="17">
@@ -16312,37 +16366,37 @@
       <c r="D139" s="20"/>
       <c r="E139" s="17"/>
       <c r="F139" s="20"/>
-      <c r="G139" s="17" t="n">
+      <c r="G139" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H139" s="17"/>
       <c r="I139" s="20"/>
       <c r="J139" s="20"/>
-      <c r="K139" s="20"/>
-      <c r="L139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P139" s="23" t="n">
+      <c r="K139" s="71"/>
+      <c r="L139" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q139" s="20"/>
-      <c r="R139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" s="20" t="n">
+      <c r="R139" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T139" s="20"/>
-      <c r="U139" s="20"/>
+      <c r="U139" s="84"/>
       <c r="V139" s="17"/>
       <c r="W139" s="20"/>
       <c r="X139" s="17">
@@ -16385,37 +16439,37 @@
       <c r="D140" s="20"/>
       <c r="E140" s="17"/>
       <c r="F140" s="20"/>
-      <c r="G140" s="17" t="n">
+      <c r="G140" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H140" s="17"/>
       <c r="I140" s="20"/>
       <c r="J140" s="20"/>
-      <c r="K140" s="20"/>
-      <c r="L140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" s="23" t="n">
+      <c r="K140" s="71"/>
+      <c r="L140" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q140" s="20"/>
-      <c r="R140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" s="20" t="n">
+      <c r="R140" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T140" s="20"/>
-      <c r="U140" s="20"/>
+      <c r="U140" s="84"/>
       <c r="V140" s="17"/>
       <c r="W140" s="20"/>
       <c r="X140" s="17">
@@ -16458,37 +16512,37 @@
       <c r="D141" s="20"/>
       <c r="E141" s="17"/>
       <c r="F141" s="20"/>
-      <c r="G141" s="17" t="n">
+      <c r="G141" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H141" s="17"/>
       <c r="I141" s="20"/>
       <c r="J141" s="20"/>
-      <c r="K141" s="20"/>
-      <c r="L141" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O141" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P141" s="23" t="n">
+      <c r="K141" s="71"/>
+      <c r="L141" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q141" s="20"/>
-      <c r="R141" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" s="20" t="n">
+      <c r="R141" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T141" s="20"/>
-      <c r="U141" s="20"/>
+      <c r="U141" s="84"/>
       <c r="V141" s="17"/>
       <c r="W141" s="20"/>
       <c r="X141" s="17">
@@ -16531,37 +16585,37 @@
       <c r="D142" s="20"/>
       <c r="E142" s="17"/>
       <c r="F142" s="20"/>
-      <c r="G142" s="17" t="n">
+      <c r="G142" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H142" s="17"/>
       <c r="I142" s="20"/>
       <c r="J142" s="20"/>
-      <c r="K142" s="20"/>
-      <c r="L142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N142" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" s="23" t="n">
+      <c r="K142" s="71"/>
+      <c r="L142" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q142" s="20"/>
-      <c r="R142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" s="20" t="n">
+      <c r="R142" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T142" s="20"/>
-      <c r="U142" s="20"/>
+      <c r="U142" s="84"/>
       <c r="V142" s="17"/>
       <c r="W142" s="20"/>
       <c r="X142" s="17">
@@ -16604,37 +16658,37 @@
       <c r="D143" s="20"/>
       <c r="E143" s="17"/>
       <c r="F143" s="20"/>
-      <c r="G143" s="17" t="n">
+      <c r="G143" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H143" s="17"/>
       <c r="I143" s="20"/>
       <c r="J143" s="20"/>
-      <c r="K143" s="20"/>
-      <c r="L143" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" s="23" t="n">
+      <c r="K143" s="71"/>
+      <c r="L143" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q143" s="20"/>
-      <c r="R143" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S143" s="20" t="n">
+      <c r="R143" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T143" s="20"/>
-      <c r="U143" s="20"/>
+      <c r="U143" s="84"/>
       <c r="V143" s="17"/>
       <c r="W143" s="20"/>
       <c r="X143" s="17">
@@ -16677,37 +16731,37 @@
       <c r="D144" s="20"/>
       <c r="E144" s="17"/>
       <c r="F144" s="20"/>
-      <c r="G144" s="17" t="n">
+      <c r="G144" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H144" s="17"/>
       <c r="I144" s="20"/>
       <c r="J144" s="20"/>
-      <c r="K144" s="20"/>
-      <c r="L144" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N144" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P144" s="23" t="n">
+      <c r="K144" s="71"/>
+      <c r="L144" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q144" s="20"/>
-      <c r="R144" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S144" s="20" t="n">
+      <c r="R144" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T144" s="20"/>
-      <c r="U144" s="20"/>
+      <c r="U144" s="84"/>
       <c r="V144" s="17"/>
       <c r="W144" s="20"/>
       <c r="X144" s="17">
@@ -16750,37 +16804,37 @@
       <c r="D145" s="20"/>
       <c r="E145" s="17"/>
       <c r="F145" s="20"/>
-      <c r="G145" s="17" t="n">
+      <c r="G145" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H145" s="17"/>
       <c r="I145" s="20"/>
       <c r="J145" s="20"/>
-      <c r="K145" s="20"/>
-      <c r="L145" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N145" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O145" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" s="23" t="n">
+      <c r="K145" s="71"/>
+      <c r="L145" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q145" s="20"/>
-      <c r="R145" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S145" s="20" t="n">
+      <c r="R145" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T145" s="20"/>
-      <c r="U145" s="20"/>
+      <c r="U145" s="84"/>
       <c r="V145" s="17"/>
       <c r="W145" s="20"/>
       <c r="X145" s="17">
@@ -16823,37 +16877,37 @@
       <c r="D146" s="20"/>
       <c r="E146" s="17"/>
       <c r="F146" s="20"/>
-      <c r="G146" s="17" t="n">
+      <c r="G146" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H146" s="17"/>
       <c r="I146" s="20"/>
       <c r="J146" s="20"/>
-      <c r="K146" s="20"/>
-      <c r="L146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N146" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" s="23" t="n">
+      <c r="K146" s="71"/>
+      <c r="L146" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q146" s="20"/>
-      <c r="R146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" s="20" t="n">
+      <c r="R146" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T146" s="20"/>
-      <c r="U146" s="20"/>
+      <c r="U146" s="84"/>
       <c r="V146" s="17"/>
       <c r="W146" s="20"/>
       <c r="X146" s="17">
@@ -16896,37 +16950,37 @@
       <c r="D147" s="20"/>
       <c r="E147" s="17"/>
       <c r="F147" s="20"/>
-      <c r="G147" s="17" t="n">
+      <c r="G147" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H147" s="17"/>
       <c r="I147" s="20"/>
       <c r="J147" s="20"/>
-      <c r="K147" s="20"/>
-      <c r="L147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" s="23" t="n">
+      <c r="K147" s="71"/>
+      <c r="L147" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q147" s="20"/>
-      <c r="R147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" s="20" t="n">
+      <c r="R147" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T147" s="20"/>
-      <c r="U147" s="20"/>
+      <c r="U147" s="84"/>
       <c r="V147" s="17"/>
       <c r="W147" s="20"/>
       <c r="X147" s="17">
@@ -16969,37 +17023,37 @@
       <c r="D148" s="20"/>
       <c r="E148" s="17"/>
       <c r="F148" s="20"/>
-      <c r="G148" s="17" t="n">
+      <c r="G148" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H148" s="17"/>
       <c r="I148" s="20"/>
       <c r="J148" s="20"/>
-      <c r="K148" s="20"/>
-      <c r="L148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" s="23" t="n">
+      <c r="K148" s="71"/>
+      <c r="L148" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q148" s="20"/>
-      <c r="R148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" s="20" t="n">
+      <c r="R148" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T148" s="20"/>
-      <c r="U148" s="20"/>
+      <c r="U148" s="84"/>
       <c r="V148" s="17"/>
       <c r="W148" s="20"/>
       <c r="X148" s="17">
@@ -17042,37 +17096,37 @@
       <c r="D149" s="20"/>
       <c r="E149" s="17"/>
       <c r="F149" s="20"/>
-      <c r="G149" s="17" t="n">
+      <c r="G149" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H149" s="17"/>
       <c r="I149" s="20"/>
       <c r="J149" s="20"/>
-      <c r="K149" s="20"/>
-      <c r="L149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N149" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P149" s="23" t="n">
+      <c r="K149" s="71"/>
+      <c r="L149" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q149" s="20"/>
-      <c r="R149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S149" s="20" t="n">
+      <c r="R149" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T149" s="20"/>
-      <c r="U149" s="20"/>
+      <c r="U149" s="84"/>
       <c r="V149" s="17"/>
       <c r="W149" s="20"/>
       <c r="X149" s="17">
@@ -17115,37 +17169,37 @@
       <c r="D150" s="20"/>
       <c r="E150" s="17"/>
       <c r="F150" s="20"/>
-      <c r="G150" s="17" t="n">
+      <c r="G150" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H150" s="17"/>
       <c r="I150" s="20"/>
       <c r="J150" s="20"/>
-      <c r="K150" s="20"/>
-      <c r="L150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N150" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P150" s="23" t="n">
+      <c r="K150" s="71"/>
+      <c r="L150" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P150" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q150" s="20"/>
-      <c r="R150" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S150" s="20" t="n">
+      <c r="R150" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S150" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T150" s="20"/>
-      <c r="U150" s="20"/>
+      <c r="U150" s="84"/>
       <c r="V150" s="17"/>
       <c r="W150" s="20"/>
       <c r="X150" s="17">
@@ -17188,37 +17242,37 @@
       <c r="D151" s="20"/>
       <c r="E151" s="17"/>
       <c r="F151" s="20"/>
-      <c r="G151" s="17" t="n">
+      <c r="G151" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H151" s="17"/>
       <c r="I151" s="20"/>
       <c r="J151" s="20"/>
-      <c r="K151" s="20"/>
-      <c r="L151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P151" s="23" t="n">
+      <c r="K151" s="71"/>
+      <c r="L151" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P151" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q151" s="20"/>
-      <c r="R151" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S151" s="20" t="n">
+      <c r="R151" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T151" s="20"/>
-      <c r="U151" s="20"/>
+      <c r="U151" s="84"/>
       <c r="V151" s="17"/>
       <c r="W151" s="20"/>
       <c r="X151" s="17">
@@ -17261,37 +17315,37 @@
       <c r="D152" s="20"/>
       <c r="E152" s="17"/>
       <c r="F152" s="20"/>
-      <c r="G152" s="17" t="n">
+      <c r="G152" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H152" s="17"/>
       <c r="I152" s="20"/>
       <c r="J152" s="20"/>
-      <c r="K152" s="20"/>
-      <c r="L152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P152" s="23" t="n">
+      <c r="K152" s="71"/>
+      <c r="L152" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q152" s="20"/>
-      <c r="R152" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S152" s="20" t="n">
+      <c r="R152" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T152" s="20"/>
-      <c r="U152" s="20"/>
+      <c r="U152" s="84"/>
       <c r="V152" s="17"/>
       <c r="W152" s="20"/>
       <c r="X152" s="17">
@@ -17334,37 +17388,37 @@
       <c r="D153" s="20"/>
       <c r="E153" s="17"/>
       <c r="F153" s="20"/>
-      <c r="G153" s="17" t="n">
+      <c r="G153" s="67" t="n">
         <v>2</v>
       </c>
       <c r="H153" s="17"/>
       <c r="I153" s="20"/>
       <c r="J153" s="20"/>
-      <c r="K153" s="20"/>
-      <c r="L153" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O153" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P153" s="23" t="n">
+      <c r="K153" s="71"/>
+      <c r="L153" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" s="76" t="n">
         <v>0</v>
       </c>
       <c r="Q153" s="20"/>
-      <c r="R153" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S153" s="20" t="n">
+      <c r="R153" s="76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" s="76" t="n">
         <v>0</v>
       </c>
       <c r="T153" s="20"/>
-      <c r="U153" s="20"/>
+      <c r="U153" s="84"/>
       <c r="V153" s="17"/>
       <c r="W153" s="20"/>
       <c r="X153" s="17">
@@ -17407,23 +17461,23 @@
       <c r="D154"/>
       <c r="E154"/>
       <c r="F154"/>
-      <c r="G154" t="n">
+      <c r="G154" s="70" t="n">
         <v>2.5</v>
       </c>
       <c r="H154"/>
       <c r="I154"/>
       <c r="J154"/>
-      <c r="K154"/>
-      <c r="L154"/>
-      <c r="M154"/>
-      <c r="N154"/>
-      <c r="O154"/>
-      <c r="P154"/>
+      <c r="K154" s="75"/>
+      <c r="L154" s="83"/>
+      <c r="M154" s="83"/>
+      <c r="N154" s="83"/>
+      <c r="O154" s="83"/>
+      <c r="P154" s="83"/>
       <c r="Q154"/>
-      <c r="R154"/>
-      <c r="S154"/>
+      <c r="R154" s="83"/>
+      <c r="S154" s="83"/>
       <c r="T154"/>
-      <c r="U154"/>
+      <c r="U154" s="88"/>
       <c r="V154"/>
       <c r="W154"/>
       <c r="X154"/>
@@ -19998,27 +20052,27 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="21">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56c30e6ca314071"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14ade19a1a1746d1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47373f4c76e34ba8"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabbf53ac66c74d87"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f6289bdd3d1412d"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0662b2e832a74010"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fded163bee8428f"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8a0159fa4d046e9"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc70ae313fc1f41f3"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf108df7022d348b8"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re77ccc151b8a4cf1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd33036ffb7214c61"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6efca91d982d4f99"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf7301c3358c4d87"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a1419b199d94145"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7eb962ab04d428b"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19eb887c46f3452f"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b1dff70014e40d1"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1783430e83404982"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf72cc711b93450c"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe38b07ba976404f"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10b19b151df640ac"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46c5238aec44f0e"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Redf1035da9e94bfb"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62029c6d9d7c4fee"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87a7b799752f4f02"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4293c98f0f204df4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6390f875ed67470b"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e127f0653034a9b"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98719a68157f4f80"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25d5a929fd1e4b5e"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe3884e9a1d4508"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb47c4d16b34fd3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd75a22d5d0674a87"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd5fe2fdfed7475c"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93e5f23aacee43b3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb027ed43abef4936"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fe993b014c045ff"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39ad4ccaaaba4faa"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4654820631854c6b"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56025d9516774788"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99754052f51e4741"/>
   </tableParts>
 </worksheet>
 </file>
@@ -23772,29 +23826,29 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="R0c6500d7d748456f"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="Rf9273de544ce49bb"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R9378b353660545be"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="R7220c58f51e1484e"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="Rdfe1d44fdcd9417e"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="R26720a3a54924cdf"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="R7f3915b9b6dc42c4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="R44a4985362bc4914"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="R8192ecb5264d4557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="Rc128d178a2914558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="Rf115d1e3b73b4f66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="R562ad10673c3466e"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="Rb5924ddc8b2c4b58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="Ra6d42153b22143ae"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="R3f512c210dc64c7f"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="R3e55e60acc1e4636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="R9868f948384e4d84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="R5a0038cb1d4b472f"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="R021a1113db1b4520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="R26e5ecd6d48c4602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="R7ba9fb530c44445a"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="R239f9552b3914ce0"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="R5c8efea364014cfc"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="Rfb3c7ae77c194597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="R617bc6b495214c6f"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="R04c2798b876f450d"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="Rd812d6c21ef24754"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="R6f7953e3c13648c8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="R1c536b83a4e847fb"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="R30c5b7d5607e42ea"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="R0288710cd5f245fd"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="R43d8cb1987124380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="R8c7e89128a234ec4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="R4924be27b34345c4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="Rd995d84df9614124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="R64ad6b0e14c64621"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6365ca4dd86d4ffc"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafef9a31cd5942e6"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1c2e978043945f8"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e3a259abe14459a"/>
   </tableParts>
 </worksheet>
 </file>